--- a/data/Fertig - 1.a_MS_misch_base/1.a_MS_misch_grid-reduced/Power_BusInfo.xlsx
+++ b/data/Fertig - 1.a_MS_misch_base/1.a_MS_misch_grid-reduced/Power_BusInfo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\01_Modelle\2025-02-24_DyLeR-20\Scenarios_1.a\1.a_MS_misch\1.a_MS_misch_base\1.a_MS_misch_grid-reduced\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tom\Tu Graz\Masterarbeit\Git\LEGO-Pyomo\data\Fertig - 1.a_MS_misch_base\1.a_MS_misch_grid-reduced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686F95D6-0397-43EB-8CF7-66D1CC13E3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15296CB3-6365-4820-A8E6-BC172C00DDA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="266">
   <si>
     <t>Power - Bus information</t>
   </si>
@@ -320,18 +320,6 @@
     <t>Netz-NÖ</t>
   </si>
   <si>
-    <t>kn001</t>
-  </si>
-  <si>
-    <t>kn002</t>
-  </si>
-  <si>
-    <t>kn005</t>
-  </si>
-  <si>
-    <t>kn006</t>
-  </si>
-  <si>
     <t>kn008</t>
   </si>
   <si>
@@ -888,6 +876,42 @@
   </si>
   <si>
     <t>Lower Voltage Softlimit  in pu</t>
+  </si>
+  <si>
+    <t>kn001_IN</t>
+  </si>
+  <si>
+    <t>kn001_PR</t>
+  </si>
+  <si>
+    <t>kn001_CO</t>
+  </si>
+  <si>
+    <t>kn002_IN</t>
+  </si>
+  <si>
+    <t>kn002_PR</t>
+  </si>
+  <si>
+    <t>kn002_CO</t>
+  </si>
+  <si>
+    <t>kn005_IN</t>
+  </si>
+  <si>
+    <t>kn005_PR</t>
+  </si>
+  <si>
+    <t>kn005_CO</t>
+  </si>
+  <si>
+    <t>kn006_IN</t>
+  </si>
+  <si>
+    <t>kn006_PR</t>
+  </si>
+  <si>
+    <t>kn006_CO</t>
   </si>
 </sst>
 </file>
@@ -1368,19 +1392,19 @@
   <sheetPr>
     <tabColor rgb="FF008080"/>
   </sheetPr>
-  <dimension ref="A1:S192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S200"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.54296875" customWidth="1"/>
-    <col min="2" max="2" width="19.7265625" customWidth="1"/>
-    <col min="3" max="12" width="15.7265625" customWidth="1"/>
-    <col min="13" max="14" width="20.1796875" customWidth="1"/>
-    <col min="15" max="16" width="15.7265625" customWidth="1"/>
-    <col min="17" max="17" width="18.7265625" customWidth="1"/>
-    <col min="18" max="19" width="24.54296875" customWidth="1"/>
+    <col min="1" max="1" width="5.5546875" customWidth="1"/>
+    <col min="2" max="2" width="19.77734375" customWidth="1"/>
+    <col min="3" max="12" width="15.77734375" customWidth="1"/>
+    <col min="13" max="14" width="20.21875" customWidth="1"/>
+    <col min="15" max="16" width="15.77734375" customWidth="1"/>
+    <col min="17" max="17" width="18.77734375" customWidth="1"/>
+    <col min="18" max="19" width="24.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1403,7 +1427,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1411,7 +1435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1434,10 +1458,10 @@
         <v>9</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>10</v>
@@ -1470,7 +1494,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
@@ -1493,10 +1517,10 @@
         <v>26</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>27</v>
@@ -1529,7 +1553,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
         <v>37</v>
@@ -1550,10 +1574,10 @@
         <v>42</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>43</v>
@@ -1586,7 +1610,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8" t="s">
         <v>51</v>
@@ -1639,7 +1663,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9" t="s">
         <v>54</v>
@@ -1692,7 +1716,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
@@ -1739,7 +1763,7 @@
       <c r="R8" s="17"/>
       <c r="S8" s="17"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
@@ -1790,11 +1814,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12" t="s">
-        <v>68</v>
+        <v>254</v>
       </c>
       <c r="D10" s="12">
         <v>1</v>
@@ -1841,11 +1865,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12" t="s">
-        <v>69</v>
+        <v>255</v>
       </c>
       <c r="D11" s="12">
         <v>1</v>
@@ -1877,10 +1901,10 @@
       <c r="M11" s="14"/>
       <c r="N11" s="14"/>
       <c r="O11" s="15">
-        <v>47.85</v>
+        <v>48.12</v>
       </c>
       <c r="P11" s="15">
-        <v>15.750769</v>
+        <v>14.716923</v>
       </c>
       <c r="Q11" s="16">
         <v>1</v>
@@ -1892,11 +1916,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12" t="s">
-        <v>70</v>
+        <v>256</v>
       </c>
       <c r="D12" s="12">
         <v>1</v>
@@ -1931,7 +1955,7 @@
         <v>48.12</v>
       </c>
       <c r="P12" s="15">
-        <v>14.790768999999999</v>
+        <v>14.716923</v>
       </c>
       <c r="Q12" s="16">
         <v>1</v>
@@ -1943,11 +1967,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12" t="s">
-        <v>71</v>
+        <v>257</v>
       </c>
       <c r="D13" s="12">
         <v>1</v>
@@ -1979,10 +2003,10 @@
       <c r="M13" s="14"/>
       <c r="N13" s="14"/>
       <c r="O13" s="15">
-        <v>48.03</v>
+        <v>47.85</v>
       </c>
       <c r="P13" s="15">
-        <v>15.603077000000001</v>
+        <v>15.750769</v>
       </c>
       <c r="Q13" s="16">
         <v>1</v>
@@ -1994,11 +2018,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="11"/>
       <c r="C14" s="12" t="s">
-        <v>72</v>
+        <v>258</v>
       </c>
       <c r="D14" s="12">
         <v>1</v>
@@ -2030,10 +2054,10 @@
       <c r="M14" s="14"/>
       <c r="N14" s="14"/>
       <c r="O14" s="15">
-        <v>48.03</v>
+        <v>47.85</v>
       </c>
       <c r="P14" s="15">
-        <v>15.713846</v>
+        <v>15.750769</v>
       </c>
       <c r="Q14" s="16">
         <v>1</v>
@@ -2045,11 +2069,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="12" t="s">
-        <v>73</v>
+        <v>259</v>
       </c>
       <c r="D15" s="12">
         <v>1</v>
@@ -2081,10 +2105,10 @@
       <c r="M15" s="14"/>
       <c r="N15" s="14"/>
       <c r="O15" s="15">
-        <v>48.12</v>
+        <v>47.85</v>
       </c>
       <c r="P15" s="15">
-        <v>15.529230999999999</v>
+        <v>15.750769</v>
       </c>
       <c r="Q15" s="16">
         <v>1</v>
@@ -2096,11 +2120,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="12" t="s">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="D16" s="12">
         <v>1</v>
@@ -2132,10 +2156,10 @@
       <c r="M16" s="14"/>
       <c r="N16" s="14"/>
       <c r="O16" s="15">
-        <v>48.3</v>
+        <v>48.12</v>
       </c>
       <c r="P16" s="15">
-        <v>15.381538000000001</v>
+        <v>14.790768999999999</v>
       </c>
       <c r="Q16" s="16">
         <v>1</v>
@@ -2147,11 +2171,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="s">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="D17" s="12">
         <v>1</v>
@@ -2183,10 +2207,10 @@
       <c r="M17" s="14"/>
       <c r="N17" s="14"/>
       <c r="O17" s="15">
-        <v>48.03</v>
+        <v>48.12</v>
       </c>
       <c r="P17" s="15">
-        <v>15.196923</v>
+        <v>14.790768999999999</v>
       </c>
       <c r="Q17" s="16">
         <v>1</v>
@@ -2198,11 +2222,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>76</v>
+        <v>262</v>
       </c>
       <c r="D18" s="12">
         <v>1</v>
@@ -2234,10 +2258,10 @@
       <c r="M18" s="14"/>
       <c r="N18" s="14"/>
       <c r="O18" s="15">
-        <v>48.03</v>
+        <v>48.12</v>
       </c>
       <c r="P18" s="15">
-        <v>15.049231000000001</v>
+        <v>14.790768999999999</v>
       </c>
       <c r="Q18" s="16">
         <v>1</v>
@@ -2249,11 +2273,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="12" t="s">
-        <v>77</v>
+        <v>263</v>
       </c>
       <c r="D19" s="12">
         <v>1</v>
@@ -2288,7 +2312,7 @@
         <v>48.03</v>
       </c>
       <c r="P19" s="15">
-        <v>15.123077</v>
+        <v>15.603077000000001</v>
       </c>
       <c r="Q19" s="16">
         <v>1</v>
@@ -2300,11 +2324,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
       <c r="C20" s="12" t="s">
-        <v>78</v>
+        <v>264</v>
       </c>
       <c r="D20" s="12">
         <v>1</v>
@@ -2336,10 +2360,10 @@
       <c r="M20" s="14"/>
       <c r="N20" s="14"/>
       <c r="O20" s="15">
-        <v>48.48</v>
+        <v>48.03</v>
       </c>
       <c r="P20" s="15">
-        <v>15.270769</v>
+        <v>15.603077000000001</v>
       </c>
       <c r="Q20" s="16">
         <v>1</v>
@@ -2351,11 +2375,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="11"/>
       <c r="C21" s="12" t="s">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="D21" s="12">
         <v>1</v>
@@ -2387,10 +2411,10 @@
       <c r="M21" s="14"/>
       <c r="N21" s="14"/>
       <c r="O21" s="15">
-        <v>48.57</v>
+        <v>48.03</v>
       </c>
       <c r="P21" s="15">
-        <v>15.049231000000001</v>
+        <v>15.603077000000001</v>
       </c>
       <c r="Q21" s="16">
         <v>1</v>
@@ -2402,11 +2426,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="11"/>
       <c r="C22" s="12" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D22" s="12">
         <v>1</v>
@@ -2438,10 +2462,10 @@
       <c r="M22" s="14"/>
       <c r="N22" s="14"/>
       <c r="O22" s="15">
-        <v>48.57</v>
+        <v>48.03</v>
       </c>
       <c r="P22" s="15">
-        <v>15.196923</v>
+        <v>15.713846</v>
       </c>
       <c r="Q22" s="16">
         <v>1</v>
@@ -2453,11 +2477,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="11"/>
       <c r="C23" s="12" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D23" s="12">
         <v>1</v>
@@ -2489,10 +2513,10 @@
       <c r="M23" s="14"/>
       <c r="N23" s="14"/>
       <c r="O23" s="15">
-        <v>48.57</v>
+        <v>48.12</v>
       </c>
       <c r="P23" s="15">
-        <v>15.16</v>
+        <v>15.529230999999999</v>
       </c>
       <c r="Q23" s="16">
         <v>1</v>
@@ -2504,11 +2528,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D24" s="12">
         <v>1</v>
@@ -2540,10 +2564,10 @@
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
       <c r="O24" s="15">
-        <v>48.21</v>
+        <v>48.3</v>
       </c>
       <c r="P24" s="15">
-        <v>15.861537999999999</v>
+        <v>15.381538000000001</v>
       </c>
       <c r="Q24" s="16">
         <v>1</v>
@@ -2555,11 +2579,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D25" s="12">
         <v>1</v>
@@ -2591,10 +2615,10 @@
       <c r="M25" s="14"/>
       <c r="N25" s="14"/>
       <c r="O25" s="15">
-        <v>48.75</v>
+        <v>48.03</v>
       </c>
       <c r="P25" s="15">
-        <v>15.270769</v>
+        <v>15.196923</v>
       </c>
       <c r="Q25" s="16">
         <v>1</v>
@@ -2606,11 +2630,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D26" s="12">
         <v>1</v>
@@ -2645,7 +2669,7 @@
         <v>48.03</v>
       </c>
       <c r="P26" s="15">
-        <v>15.270769</v>
+        <v>15.049231000000001</v>
       </c>
       <c r="Q26" s="16">
         <v>1</v>
@@ -2657,11 +2681,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D27" s="12">
         <v>1</v>
@@ -2693,10 +2717,10 @@
       <c r="M27" s="14"/>
       <c r="N27" s="14"/>
       <c r="O27" s="15">
-        <v>48.66</v>
+        <v>48.03</v>
       </c>
       <c r="P27" s="15">
-        <v>14.938461999999999</v>
+        <v>15.123077</v>
       </c>
       <c r="Q27" s="16">
         <v>1</v>
@@ -2708,11 +2732,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D28" s="12">
         <v>1</v>
@@ -2744,10 +2768,10 @@
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
       <c r="O28" s="15">
-        <v>48.39</v>
+        <v>48.48</v>
       </c>
       <c r="P28" s="15">
-        <v>15.750769</v>
+        <v>15.270769</v>
       </c>
       <c r="Q28" s="16">
         <v>1</v>
@@ -2759,11 +2783,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D29" s="12">
         <v>1</v>
@@ -2795,10 +2819,10 @@
       <c r="M29" s="14"/>
       <c r="N29" s="14"/>
       <c r="O29" s="15">
-        <v>48.39</v>
+        <v>48.57</v>
       </c>
       <c r="P29" s="15">
-        <v>15.824615</v>
+        <v>15.049231000000001</v>
       </c>
       <c r="Q29" s="16">
         <v>1</v>
@@ -2810,11 +2834,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D30" s="12">
         <v>1</v>
@@ -2846,10 +2870,10 @@
       <c r="M30" s="14"/>
       <c r="N30" s="14"/>
       <c r="O30" s="15">
-        <v>48.03</v>
+        <v>48.57</v>
       </c>
       <c r="P30" s="15">
-        <v>15.455385</v>
+        <v>15.196923</v>
       </c>
       <c r="Q30" s="16">
         <v>1</v>
@@ -2861,11 +2885,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="12" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D31" s="12">
         <v>1</v>
@@ -2897,10 +2921,10 @@
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
       <c r="O31" s="15">
-        <v>48.3</v>
+        <v>48.57</v>
       </c>
       <c r="P31" s="15">
-        <v>15.529230999999999</v>
+        <v>15.16</v>
       </c>
       <c r="Q31" s="16">
         <v>1</v>
@@ -2912,11 +2936,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D32" s="12">
         <v>1</v>
@@ -2948,10 +2972,10 @@
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
       <c r="O32" s="15">
-        <v>48.12</v>
+        <v>48.21</v>
       </c>
       <c r="P32" s="15">
-        <v>15.381538000000001</v>
+        <v>15.861537999999999</v>
       </c>
       <c r="Q32" s="16">
         <v>1</v>
@@ -2963,11 +2987,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D33" s="12">
         <v>1</v>
@@ -2999,10 +3023,10 @@
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
       <c r="O33" s="15">
-        <v>48.57</v>
+        <v>48.75</v>
       </c>
       <c r="P33" s="15">
-        <v>15.307691999999999</v>
+        <v>15.270769</v>
       </c>
       <c r="Q33" s="16">
         <v>1</v>
@@ -3014,11 +3038,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="12" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D34" s="12">
         <v>1</v>
@@ -3050,10 +3074,10 @@
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
       <c r="O34" s="15">
-        <v>47.94</v>
+        <v>48.03</v>
       </c>
       <c r="P34" s="15">
-        <v>15.713846</v>
+        <v>15.270769</v>
       </c>
       <c r="Q34" s="16">
         <v>1</v>
@@ -3065,11 +3089,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D35" s="12">
         <v>1</v>
@@ -3101,10 +3125,10 @@
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
       <c r="O35" s="15">
-        <v>48.3</v>
+        <v>48.66</v>
       </c>
       <c r="P35" s="15">
-        <v>15.123077</v>
+        <v>14.938461999999999</v>
       </c>
       <c r="Q35" s="16">
         <v>1</v>
@@ -3116,11 +3140,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D36" s="12">
         <v>1</v>
@@ -3152,10 +3176,10 @@
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
       <c r="O36" s="15">
-        <v>48.48</v>
+        <v>48.39</v>
       </c>
       <c r="P36" s="15">
-        <v>15.16</v>
+        <v>15.750769</v>
       </c>
       <c r="Q36" s="16">
         <v>1</v>
@@ -3167,11 +3191,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D37" s="12">
         <v>1</v>
@@ -3206,7 +3230,7 @@
         <v>48.39</v>
       </c>
       <c r="P37" s="15">
-        <v>14.68</v>
+        <v>15.824615</v>
       </c>
       <c r="Q37" s="16">
         <v>1</v>
@@ -3218,11 +3242,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="11"/>
       <c r="C38" s="12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D38" s="12">
         <v>1</v>
@@ -3254,10 +3278,10 @@
       <c r="M38" s="14"/>
       <c r="N38" s="14"/>
       <c r="O38" s="15">
-        <v>48.66</v>
+        <v>48.03</v>
       </c>
       <c r="P38" s="15">
-        <v>15.381538000000001</v>
+        <v>15.455385</v>
       </c>
       <c r="Q38" s="16">
         <v>1</v>
@@ -3269,11 +3293,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D39" s="12">
         <v>1</v>
@@ -3305,10 +3329,10 @@
       <c r="M39" s="14"/>
       <c r="N39" s="14"/>
       <c r="O39" s="15">
-        <v>48.48</v>
+        <v>48.3</v>
       </c>
       <c r="P39" s="15">
-        <v>15.086154000000001</v>
+        <v>15.529230999999999</v>
       </c>
       <c r="Q39" s="16">
         <v>1</v>
@@ -3320,11 +3344,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D40" s="12">
         <v>1</v>
@@ -3356,10 +3380,10 @@
       <c r="M40" s="14"/>
       <c r="N40" s="14"/>
       <c r="O40" s="15">
-        <v>48.21</v>
+        <v>48.12</v>
       </c>
       <c r="P40" s="15">
-        <v>15.64</v>
+        <v>15.381538000000001</v>
       </c>
       <c r="Q40" s="16">
         <v>1</v>
@@ -3371,11 +3395,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="10"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D41" s="12">
         <v>1</v>
@@ -3407,10 +3431,10 @@
       <c r="M41" s="14"/>
       <c r="N41" s="14"/>
       <c r="O41" s="15">
-        <v>48.39</v>
+        <v>48.57</v>
       </c>
       <c r="P41" s="15">
-        <v>14.901538</v>
+        <v>15.307691999999999</v>
       </c>
       <c r="Q41" s="16">
         <v>1</v>
@@ -3422,11 +3446,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="10"/>
       <c r="B42" s="11"/>
       <c r="C42" s="12" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D42" s="12">
         <v>1</v>
@@ -3458,7 +3482,7 @@
       <c r="M42" s="14"/>
       <c r="N42" s="14"/>
       <c r="O42" s="15">
-        <v>48.12</v>
+        <v>47.94</v>
       </c>
       <c r="P42" s="15">
         <v>15.713846</v>
@@ -3473,11 +3497,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D43" s="12">
         <v>1</v>
@@ -3512,7 +3536,7 @@
         <v>48.3</v>
       </c>
       <c r="P43" s="15">
-        <v>15.64</v>
+        <v>15.123077</v>
       </c>
       <c r="Q43" s="16">
         <v>1</v>
@@ -3524,11 +3548,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D44" s="12">
         <v>1</v>
@@ -3560,10 +3584,10 @@
       <c r="M44" s="14"/>
       <c r="N44" s="14"/>
       <c r="O44" s="15">
-        <v>48.12</v>
+        <v>48.48</v>
       </c>
       <c r="P44" s="15">
-        <v>14.938461999999999</v>
+        <v>15.16</v>
       </c>
       <c r="Q44" s="16">
         <v>1</v>
@@ -3575,11 +3599,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
       <c r="B45" s="11"/>
       <c r="C45" s="12" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D45" s="12">
         <v>1</v>
@@ -3611,10 +3635,10 @@
       <c r="M45" s="14"/>
       <c r="N45" s="14"/>
       <c r="O45" s="15">
-        <v>48.48</v>
+        <v>48.39</v>
       </c>
       <c r="P45" s="15">
-        <v>15.233846</v>
+        <v>14.68</v>
       </c>
       <c r="Q45" s="16">
         <v>1</v>
@@ -3626,11 +3650,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
       <c r="B46" s="11"/>
       <c r="C46" s="12" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D46" s="12">
         <v>1</v>
@@ -3662,10 +3686,10 @@
       <c r="M46" s="14"/>
       <c r="N46" s="14"/>
       <c r="O46" s="15">
-        <v>48.12</v>
+        <v>48.66</v>
       </c>
       <c r="P46" s="15">
-        <v>14.827692000000001</v>
+        <v>15.381538000000001</v>
       </c>
       <c r="Q46" s="16">
         <v>1</v>
@@ -3677,11 +3701,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="10"/>
       <c r="B47" s="11"/>
       <c r="C47" s="12" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D47" s="12">
         <v>1</v>
@@ -3713,10 +3737,10 @@
       <c r="M47" s="14"/>
       <c r="N47" s="14"/>
       <c r="O47" s="15">
-        <v>48.57</v>
+        <v>48.48</v>
       </c>
       <c r="P47" s="15">
-        <v>15.344614999999999</v>
+        <v>15.086154000000001</v>
       </c>
       <c r="Q47" s="16">
         <v>1</v>
@@ -3728,11 +3752,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="10"/>
       <c r="B48" s="11"/>
       <c r="C48" s="12" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D48" s="12">
         <v>1</v>
@@ -3764,10 +3788,10 @@
       <c r="M48" s="14"/>
       <c r="N48" s="14"/>
       <c r="O48" s="15">
-        <v>48.03</v>
+        <v>48.21</v>
       </c>
       <c r="P48" s="15">
-        <v>15.676923</v>
+        <v>15.64</v>
       </c>
       <c r="Q48" s="16">
         <v>1</v>
@@ -3779,11 +3803,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="10"/>
       <c r="B49" s="11"/>
       <c r="C49" s="12" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D49" s="12">
         <v>1</v>
@@ -3815,10 +3839,10 @@
       <c r="M49" s="14"/>
       <c r="N49" s="14"/>
       <c r="O49" s="15">
-        <v>48.03</v>
+        <v>48.39</v>
       </c>
       <c r="P49" s="15">
-        <v>15.012308000000001</v>
+        <v>14.901538</v>
       </c>
       <c r="Q49" s="16">
         <v>1</v>
@@ -3830,11 +3854,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="10"/>
       <c r="B50" s="11"/>
       <c r="C50" s="12" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D50" s="12">
         <v>1</v>
@@ -3866,10 +3890,10 @@
       <c r="M50" s="14"/>
       <c r="N50" s="14"/>
       <c r="O50" s="15">
-        <v>48.57</v>
+        <v>48.12</v>
       </c>
       <c r="P50" s="15">
-        <v>15.64</v>
+        <v>15.713846</v>
       </c>
       <c r="Q50" s="16">
         <v>1</v>
@@ -3881,11 +3905,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="10"/>
       <c r="B51" s="11"/>
       <c r="C51" s="12" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D51" s="12">
         <v>1</v>
@@ -3917,10 +3941,10 @@
       <c r="M51" s="14"/>
       <c r="N51" s="14"/>
       <c r="O51" s="15">
-        <v>48.66</v>
+        <v>48.3</v>
       </c>
       <c r="P51" s="15">
-        <v>15.418462</v>
+        <v>15.64</v>
       </c>
       <c r="Q51" s="16">
         <v>1</v>
@@ -3932,11 +3956,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
       <c r="B52" s="11"/>
       <c r="C52" s="12" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D52" s="12">
         <v>1</v>
@@ -3968,10 +3992,10 @@
       <c r="M52" s="14"/>
       <c r="N52" s="14"/>
       <c r="O52" s="15">
-        <v>48.39</v>
+        <v>48.12</v>
       </c>
       <c r="P52" s="15">
-        <v>15.196923</v>
+        <v>14.938461999999999</v>
       </c>
       <c r="Q52" s="16">
         <v>1</v>
@@ -3983,11 +4007,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="10"/>
       <c r="B53" s="11"/>
       <c r="C53" s="12" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D53" s="12">
         <v>1</v>
@@ -4019,10 +4043,10 @@
       <c r="M53" s="14"/>
       <c r="N53" s="14"/>
       <c r="O53" s="15">
-        <v>48.3</v>
+        <v>48.48</v>
       </c>
       <c r="P53" s="15">
-        <v>15.196923</v>
+        <v>15.233846</v>
       </c>
       <c r="Q53" s="16">
         <v>1</v>
@@ -4034,11 +4058,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="10"/>
       <c r="B54" s="11"/>
       <c r="C54" s="12" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D54" s="12">
         <v>1</v>
@@ -4070,10 +4094,10 @@
       <c r="M54" s="14"/>
       <c r="N54" s="14"/>
       <c r="O54" s="15">
-        <v>48.66</v>
+        <v>48.12</v>
       </c>
       <c r="P54" s="15">
-        <v>15.196923</v>
+        <v>14.827692000000001</v>
       </c>
       <c r="Q54" s="16">
         <v>1</v>
@@ -4085,11 +4109,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="10"/>
       <c r="B55" s="11"/>
       <c r="C55" s="12" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D55" s="12">
         <v>1</v>
@@ -4121,10 +4145,10 @@
       <c r="M55" s="14"/>
       <c r="N55" s="14"/>
       <c r="O55" s="15">
-        <v>48.3</v>
+        <v>48.57</v>
       </c>
       <c r="P55" s="15">
-        <v>15.492308</v>
+        <v>15.344614999999999</v>
       </c>
       <c r="Q55" s="16">
         <v>1</v>
@@ -4136,11 +4160,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="10"/>
       <c r="B56" s="11"/>
       <c r="C56" s="12" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D56" s="12">
         <v>1</v>
@@ -4172,10 +4196,10 @@
       <c r="M56" s="14"/>
       <c r="N56" s="14"/>
       <c r="O56" s="15">
-        <v>48.39</v>
+        <v>48.03</v>
       </c>
       <c r="P56" s="15">
-        <v>15.529230999999999</v>
+        <v>15.676923</v>
       </c>
       <c r="Q56" s="16">
         <v>1</v>
@@ -4187,11 +4211,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="10"/>
       <c r="B57" s="11"/>
       <c r="C57" s="12" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D57" s="12">
         <v>1</v>
@@ -4223,10 +4247,10 @@
       <c r="M57" s="14"/>
       <c r="N57" s="14"/>
       <c r="O57" s="15">
-        <v>48.12</v>
+        <v>48.03</v>
       </c>
       <c r="P57" s="15">
-        <v>15.824615</v>
+        <v>15.012308000000001</v>
       </c>
       <c r="Q57" s="16">
         <v>1</v>
@@ -4238,11 +4262,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="10"/>
       <c r="B58" s="11"/>
       <c r="C58" s="12" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D58" s="12">
         <v>1</v>
@@ -4277,7 +4301,7 @@
         <v>48.57</v>
       </c>
       <c r="P58" s="15">
-        <v>15.418462</v>
+        <v>15.64</v>
       </c>
       <c r="Q58" s="16">
         <v>1</v>
@@ -4289,11 +4313,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="10"/>
       <c r="B59" s="11"/>
       <c r="C59" s="12" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D59" s="12">
         <v>1</v>
@@ -4325,10 +4349,10 @@
       <c r="M59" s="14"/>
       <c r="N59" s="14"/>
       <c r="O59" s="15">
-        <v>48.57</v>
+        <v>48.66</v>
       </c>
       <c r="P59" s="15">
-        <v>15.012308000000001</v>
+        <v>15.418462</v>
       </c>
       <c r="Q59" s="16">
         <v>1</v>
@@ -4340,11 +4364,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="10"/>
       <c r="B60" s="11"/>
       <c r="C60" s="12" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D60" s="12">
         <v>1</v>
@@ -4376,10 +4400,10 @@
       <c r="M60" s="14"/>
       <c r="N60" s="14"/>
       <c r="O60" s="15">
-        <v>48.66</v>
+        <v>48.39</v>
       </c>
       <c r="P60" s="15">
-        <v>15.16</v>
+        <v>15.196923</v>
       </c>
       <c r="Q60" s="16">
         <v>1</v>
@@ -4391,11 +4415,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="10"/>
       <c r="B61" s="11"/>
       <c r="C61" s="12" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D61" s="12">
         <v>1</v>
@@ -4427,10 +4451,10 @@
       <c r="M61" s="14"/>
       <c r="N61" s="14"/>
       <c r="O61" s="15">
-        <v>48.48</v>
+        <v>48.3</v>
       </c>
       <c r="P61" s="15">
-        <v>15.603077000000001</v>
+        <v>15.196923</v>
       </c>
       <c r="Q61" s="16">
         <v>1</v>
@@ -4442,11 +4466,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="10"/>
       <c r="B62" s="11"/>
       <c r="C62" s="12" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D62" s="12">
         <v>1</v>
@@ -4478,10 +4502,10 @@
       <c r="M62" s="14"/>
       <c r="N62" s="14"/>
       <c r="O62" s="15">
-        <v>48.48</v>
+        <v>48.66</v>
       </c>
       <c r="P62" s="15">
-        <v>15.123077</v>
+        <v>15.196923</v>
       </c>
       <c r="Q62" s="16">
         <v>1</v>
@@ -4493,11 +4517,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="10"/>
       <c r="B63" s="11"/>
       <c r="C63" s="12" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D63" s="12">
         <v>1</v>
@@ -4529,10 +4553,10 @@
       <c r="M63" s="14"/>
       <c r="N63" s="14"/>
       <c r="O63" s="15">
-        <v>48.03</v>
+        <v>48.3</v>
       </c>
       <c r="P63" s="15">
-        <v>15.787692</v>
+        <v>15.492308</v>
       </c>
       <c r="Q63" s="16">
         <v>1</v>
@@ -4544,11 +4568,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
       <c r="B64" s="11"/>
       <c r="C64" s="12" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D64" s="12">
         <v>1</v>
@@ -4580,10 +4604,10 @@
       <c r="M64" s="14"/>
       <c r="N64" s="14"/>
       <c r="O64" s="15">
-        <v>48.12</v>
+        <v>48.39</v>
       </c>
       <c r="P64" s="15">
-        <v>15.16</v>
+        <v>15.529230999999999</v>
       </c>
       <c r="Q64" s="16">
         <v>1</v>
@@ -4595,11 +4619,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="10"/>
       <c r="B65" s="11"/>
       <c r="C65" s="12" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D65" s="12">
         <v>1</v>
@@ -4631,10 +4655,10 @@
       <c r="M65" s="14"/>
       <c r="N65" s="14"/>
       <c r="O65" s="15">
-        <v>48.03</v>
+        <v>48.12</v>
       </c>
       <c r="P65" s="15">
-        <v>16.046154000000001</v>
+        <v>15.824615</v>
       </c>
       <c r="Q65" s="16">
         <v>1</v>
@@ -4646,11 +4670,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="10"/>
       <c r="B66" s="11"/>
       <c r="C66" s="12" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D66" s="12">
         <v>1</v>
@@ -4682,10 +4706,10 @@
       <c r="M66" s="14"/>
       <c r="N66" s="14"/>
       <c r="O66" s="15">
-        <v>48.75</v>
+        <v>48.57</v>
       </c>
       <c r="P66" s="15">
-        <v>15.455385</v>
+        <v>15.418462</v>
       </c>
       <c r="Q66" s="16">
         <v>1</v>
@@ -4697,11 +4721,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="10"/>
       <c r="B67" s="11"/>
       <c r="C67" s="12" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D67" s="12">
         <v>1</v>
@@ -4733,10 +4757,10 @@
       <c r="M67" s="14"/>
       <c r="N67" s="14"/>
       <c r="O67" s="15">
-        <v>48.03</v>
+        <v>48.57</v>
       </c>
       <c r="P67" s="15">
-        <v>15.861537999999999</v>
+        <v>15.012308000000001</v>
       </c>
       <c r="Q67" s="16">
         <v>1</v>
@@ -4748,11 +4772,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="10"/>
       <c r="B68" s="11"/>
       <c r="C68" s="12" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D68" s="12">
         <v>1</v>
@@ -4784,10 +4808,10 @@
       <c r="M68" s="14"/>
       <c r="N68" s="14"/>
       <c r="O68" s="15">
-        <v>48.3</v>
+        <v>48.66</v>
       </c>
       <c r="P68" s="15">
-        <v>15.713846</v>
+        <v>15.16</v>
       </c>
       <c r="Q68" s="16">
         <v>1</v>
@@ -4799,11 +4823,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="10"/>
       <c r="B69" s="11"/>
       <c r="C69" s="12" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D69" s="12">
         <v>1</v>
@@ -4835,10 +4859,10 @@
       <c r="M69" s="14"/>
       <c r="N69" s="14"/>
       <c r="O69" s="15">
-        <v>48.75</v>
+        <v>48.48</v>
       </c>
       <c r="P69" s="15">
-        <v>14.901538</v>
+        <v>15.603077000000001</v>
       </c>
       <c r="Q69" s="16">
         <v>1</v>
@@ -4850,11 +4874,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="11"/>
       <c r="C70" s="12" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D70" s="12">
         <v>1</v>
@@ -4886,10 +4910,10 @@
       <c r="M70" s="14"/>
       <c r="N70" s="14"/>
       <c r="O70" s="15">
-        <v>48.57</v>
+        <v>48.48</v>
       </c>
       <c r="P70" s="15">
-        <v>15.455385</v>
+        <v>15.123077</v>
       </c>
       <c r="Q70" s="16">
         <v>1</v>
@@ -4901,11 +4925,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="10"/>
       <c r="B71" s="11"/>
       <c r="C71" s="12" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D71" s="12">
         <v>1</v>
@@ -4937,10 +4961,10 @@
       <c r="M71" s="14"/>
       <c r="N71" s="14"/>
       <c r="O71" s="15">
-        <v>48.12</v>
+        <v>48.03</v>
       </c>
       <c r="P71" s="15">
-        <v>15.566153999999999</v>
+        <v>15.787692</v>
       </c>
       <c r="Q71" s="16">
         <v>1</v>
@@ -4952,11 +4976,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="10"/>
       <c r="B72" s="11"/>
       <c r="C72" s="12" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D72" s="12">
         <v>1</v>
@@ -4988,10 +5012,10 @@
       <c r="M72" s="14"/>
       <c r="N72" s="14"/>
       <c r="O72" s="15">
-        <v>48.48</v>
+        <v>48.12</v>
       </c>
       <c r="P72" s="15">
-        <v>15.012308000000001</v>
+        <v>15.16</v>
       </c>
       <c r="Q72" s="16">
         <v>1</v>
@@ -5003,11 +5027,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="10"/>
       <c r="B73" s="11"/>
       <c r="C73" s="12" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D73" s="12">
         <v>1</v>
@@ -5039,10 +5063,10 @@
       <c r="M73" s="14"/>
       <c r="N73" s="14"/>
       <c r="O73" s="15">
-        <v>48.48</v>
+        <v>48.03</v>
       </c>
       <c r="P73" s="15">
-        <v>15.307691999999999</v>
+        <v>16.046154000000001</v>
       </c>
       <c r="Q73" s="16">
         <v>1</v>
@@ -5054,11 +5078,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="10"/>
       <c r="B74" s="11"/>
       <c r="C74" s="12" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D74" s="12">
         <v>1</v>
@@ -5090,10 +5114,10 @@
       <c r="M74" s="14"/>
       <c r="N74" s="14"/>
       <c r="O74" s="15">
-        <v>48.39</v>
+        <v>48.75</v>
       </c>
       <c r="P74" s="15">
-        <v>14.975384999999999</v>
+        <v>15.455385</v>
       </c>
       <c r="Q74" s="16">
         <v>1</v>
@@ -5105,11 +5129,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="10"/>
       <c r="B75" s="11"/>
       <c r="C75" s="12" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D75" s="12">
         <v>1</v>
@@ -5141,10 +5165,10 @@
       <c r="M75" s="14"/>
       <c r="N75" s="14"/>
       <c r="O75" s="15">
-        <v>48.48</v>
+        <v>48.03</v>
       </c>
       <c r="P75" s="15">
-        <v>15.492308</v>
+        <v>15.861537999999999</v>
       </c>
       <c r="Q75" s="16">
         <v>1</v>
@@ -5156,11 +5180,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="10"/>
       <c r="B76" s="11"/>
       <c r="C76" s="12" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="D76" s="12">
         <v>1</v>
@@ -5192,10 +5216,10 @@
       <c r="M76" s="14"/>
       <c r="N76" s="14"/>
       <c r="O76" s="15">
-        <v>48.66</v>
+        <v>48.3</v>
       </c>
       <c r="P76" s="15">
-        <v>15.307691999999999</v>
+        <v>15.713846</v>
       </c>
       <c r="Q76" s="16">
         <v>1</v>
@@ -5207,11 +5231,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="10"/>
       <c r="B77" s="11"/>
       <c r="C77" s="12" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D77" s="12">
         <v>1</v>
@@ -5243,10 +5267,10 @@
       <c r="M77" s="14"/>
       <c r="N77" s="14"/>
       <c r="O77" s="15">
-        <v>48.12</v>
+        <v>48.75</v>
       </c>
       <c r="P77" s="15">
-        <v>14.864615000000001</v>
+        <v>14.901538</v>
       </c>
       <c r="Q77" s="16">
         <v>1</v>
@@ -5258,11 +5282,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="10"/>
       <c r="B78" s="11"/>
       <c r="C78" s="12" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="D78" s="12">
         <v>1</v>
@@ -5294,10 +5318,10 @@
       <c r="M78" s="14"/>
       <c r="N78" s="14"/>
       <c r="O78" s="15">
-        <v>48.21</v>
+        <v>48.57</v>
       </c>
       <c r="P78" s="15">
-        <v>14.827692000000001</v>
+        <v>15.455385</v>
       </c>
       <c r="Q78" s="16">
         <v>1</v>
@@ -5309,11 +5333,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="10"/>
       <c r="B79" s="11"/>
       <c r="C79" s="12" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D79" s="12">
         <v>1</v>
@@ -5345,10 +5369,10 @@
       <c r="M79" s="14"/>
       <c r="N79" s="14"/>
       <c r="O79" s="15">
-        <v>48.57</v>
+        <v>48.12</v>
       </c>
       <c r="P79" s="15">
-        <v>15.270769</v>
+        <v>15.566153999999999</v>
       </c>
       <c r="Q79" s="16">
         <v>1</v>
@@ -5360,11 +5384,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="10"/>
       <c r="B80" s="11"/>
       <c r="C80" s="12" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D80" s="12">
         <v>1</v>
@@ -5396,10 +5420,10 @@
       <c r="M80" s="14"/>
       <c r="N80" s="14"/>
       <c r="O80" s="15">
-        <v>48.57</v>
+        <v>48.48</v>
       </c>
       <c r="P80" s="15">
-        <v>14.864615000000001</v>
+        <v>15.012308000000001</v>
       </c>
       <c r="Q80" s="16">
         <v>1</v>
@@ -5411,11 +5435,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" s="10"/>
       <c r="B81" s="11"/>
       <c r="C81" s="12" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D81" s="12">
         <v>1</v>
@@ -5447,10 +5471,10 @@
       <c r="M81" s="14"/>
       <c r="N81" s="14"/>
       <c r="O81" s="15">
-        <v>48.12</v>
+        <v>48.48</v>
       </c>
       <c r="P81" s="15">
-        <v>15.861537999999999</v>
+        <v>15.307691999999999</v>
       </c>
       <c r="Q81" s="16">
         <v>1</v>
@@ -5462,11 +5486,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" s="10"/>
       <c r="B82" s="11"/>
       <c r="C82" s="12" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D82" s="12">
         <v>1</v>
@@ -5501,7 +5525,7 @@
         <v>48.39</v>
       </c>
       <c r="P82" s="15">
-        <v>14.716923</v>
+        <v>14.975384999999999</v>
       </c>
       <c r="Q82" s="16">
         <v>1</v>
@@ -5513,11 +5537,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" s="10"/>
       <c r="B83" s="11"/>
       <c r="C83" s="12" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D83" s="12">
         <v>1</v>
@@ -5549,10 +5573,10 @@
       <c r="M83" s="14"/>
       <c r="N83" s="14"/>
       <c r="O83" s="15">
-        <v>47.85</v>
+        <v>48.48</v>
       </c>
       <c r="P83" s="15">
-        <v>15.233846</v>
+        <v>15.492308</v>
       </c>
       <c r="Q83" s="16">
         <v>1</v>
@@ -5564,11 +5588,11 @@
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" s="10"/>
       <c r="B84" s="11"/>
       <c r="C84" s="12" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D84" s="12">
         <v>1</v>
@@ -5600,26 +5624,26 @@
       <c r="M84" s="14"/>
       <c r="N84" s="14"/>
       <c r="O84" s="15">
-        <v>47.94</v>
+        <v>48.66</v>
       </c>
       <c r="P84" s="15">
-        <v>15.16</v>
+        <v>15.307691999999999</v>
       </c>
       <c r="Q84" s="16">
         <v>1</v>
       </c>
       <c r="R84" s="17" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="S84" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" s="10"/>
       <c r="B85" s="11"/>
       <c r="C85" s="12" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="D85" s="12">
         <v>1</v>
@@ -5651,26 +5675,26 @@
       <c r="M85" s="14"/>
       <c r="N85" s="14"/>
       <c r="O85" s="15">
-        <v>48.48</v>
+        <v>48.12</v>
       </c>
       <c r="P85" s="15">
-        <v>15.381538000000001</v>
+        <v>14.864615000000001</v>
       </c>
       <c r="Q85" s="16">
         <v>1</v>
       </c>
       <c r="R85" s="17" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="S85" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" s="10"/>
       <c r="B86" s="11"/>
       <c r="C86" s="12" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D86" s="12">
         <v>1</v>
@@ -5702,26 +5726,26 @@
       <c r="M86" s="14"/>
       <c r="N86" s="14"/>
       <c r="O86" s="15">
-        <v>48.3</v>
+        <v>48.21</v>
       </c>
       <c r="P86" s="15">
-        <v>14.790768999999999</v>
+        <v>14.827692000000001</v>
       </c>
       <c r="Q86" s="16">
         <v>1</v>
       </c>
       <c r="R86" s="17" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="S86" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87" s="10"/>
       <c r="B87" s="11"/>
       <c r="C87" s="12" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D87" s="12">
         <v>1</v>
@@ -5753,26 +5777,26 @@
       <c r="M87" s="14"/>
       <c r="N87" s="14"/>
       <c r="O87" s="15">
-        <v>48.3</v>
+        <v>48.57</v>
       </c>
       <c r="P87" s="15">
-        <v>15.566153999999999</v>
+        <v>15.270769</v>
       </c>
       <c r="Q87" s="16">
         <v>1</v>
       </c>
       <c r="R87" s="17" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="S87" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
       <c r="B88" s="11"/>
       <c r="C88" s="12" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D88" s="12">
         <v>1</v>
@@ -5804,26 +5828,26 @@
       <c r="M88" s="14"/>
       <c r="N88" s="14"/>
       <c r="O88" s="15">
-        <v>48.03</v>
+        <v>48.57</v>
       </c>
       <c r="P88" s="15">
-        <v>15.898462</v>
+        <v>14.864615000000001</v>
       </c>
       <c r="Q88" s="16">
         <v>1</v>
       </c>
       <c r="R88" s="17" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="S88" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
       <c r="B89" s="11"/>
       <c r="C89" s="12" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="D89" s="12">
         <v>1</v>
@@ -5855,26 +5879,26 @@
       <c r="M89" s="14"/>
       <c r="N89" s="14"/>
       <c r="O89" s="15">
-        <v>48.39</v>
+        <v>48.12</v>
       </c>
       <c r="P89" s="15">
-        <v>15.566153999999999</v>
+        <v>15.861537999999999</v>
       </c>
       <c r="Q89" s="16">
         <v>1</v>
       </c>
       <c r="R89" s="17" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="S89" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A90" s="10"/>
       <c r="B90" s="11"/>
       <c r="C90" s="12" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D90" s="12">
         <v>1</v>
@@ -5906,26 +5930,26 @@
       <c r="M90" s="14"/>
       <c r="N90" s="14"/>
       <c r="O90" s="15">
-        <v>48.21</v>
+        <v>48.39</v>
       </c>
       <c r="P90" s="15">
-        <v>15.16</v>
+        <v>14.716923</v>
       </c>
       <c r="Q90" s="16">
         <v>1</v>
       </c>
       <c r="R90" s="17" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="S90" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A91" s="10"/>
       <c r="B91" s="11"/>
       <c r="C91" s="12" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D91" s="12">
         <v>1</v>
@@ -5957,26 +5981,26 @@
       <c r="M91" s="14"/>
       <c r="N91" s="14"/>
       <c r="O91" s="15">
-        <v>48.75</v>
+        <v>47.85</v>
       </c>
       <c r="P91" s="15">
-        <v>15.344614999999999</v>
+        <v>15.233846</v>
       </c>
       <c r="Q91" s="16">
         <v>1</v>
       </c>
       <c r="R91" s="17" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="S91" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A92" s="10"/>
       <c r="B92" s="11"/>
       <c r="C92" s="12" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D92" s="12">
         <v>1</v>
@@ -6008,26 +6032,26 @@
       <c r="M92" s="14"/>
       <c r="N92" s="14"/>
       <c r="O92" s="15">
-        <v>48.48</v>
+        <v>47.94</v>
       </c>
       <c r="P92" s="15">
-        <v>14.901538</v>
+        <v>15.16</v>
       </c>
       <c r="Q92" s="16">
         <v>1</v>
       </c>
       <c r="R92" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S92" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A93" s="10"/>
       <c r="B93" s="11"/>
       <c r="C93" s="12" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D93" s="12">
         <v>1</v>
@@ -6059,26 +6083,26 @@
       <c r="M93" s="14"/>
       <c r="N93" s="14"/>
       <c r="O93" s="15">
-        <v>47.94</v>
+        <v>48.48</v>
       </c>
       <c r="P93" s="15">
-        <v>15.123077</v>
+        <v>15.381538000000001</v>
       </c>
       <c r="Q93" s="16">
         <v>1</v>
       </c>
       <c r="R93" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S93" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A94" s="10"/>
       <c r="B94" s="11"/>
       <c r="C94" s="12" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D94" s="12">
         <v>1</v>
@@ -6110,26 +6134,26 @@
       <c r="M94" s="14"/>
       <c r="N94" s="14"/>
       <c r="O94" s="15">
-        <v>48.75</v>
+        <v>48.3</v>
       </c>
       <c r="P94" s="15">
-        <v>15.196923</v>
+        <v>14.790768999999999</v>
       </c>
       <c r="Q94" s="16">
         <v>1</v>
       </c>
       <c r="R94" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S94" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A95" s="10"/>
       <c r="B95" s="11"/>
       <c r="C95" s="12" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="D95" s="12">
         <v>1</v>
@@ -6161,26 +6185,26 @@
       <c r="M95" s="14"/>
       <c r="N95" s="14"/>
       <c r="O95" s="15">
-        <v>48.39</v>
+        <v>48.3</v>
       </c>
       <c r="P95" s="15">
-        <v>15.898462</v>
+        <v>15.566153999999999</v>
       </c>
       <c r="Q95" s="16">
         <v>1</v>
       </c>
       <c r="R95" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S95" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A96" s="10"/>
       <c r="B96" s="11"/>
       <c r="C96" s="12" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="D96" s="12">
         <v>1</v>
@@ -6212,26 +6236,26 @@
       <c r="M96" s="14"/>
       <c r="N96" s="14"/>
       <c r="O96" s="15">
-        <v>48.75</v>
+        <v>48.03</v>
       </c>
       <c r="P96" s="15">
-        <v>15.233846</v>
+        <v>15.898462</v>
       </c>
       <c r="Q96" s="16">
         <v>1</v>
       </c>
       <c r="R96" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S96" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="10"/>
       <c r="B97" s="11"/>
       <c r="C97" s="12" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D97" s="12">
         <v>1</v>
@@ -6263,26 +6287,26 @@
       <c r="M97" s="14"/>
       <c r="N97" s="14"/>
       <c r="O97" s="15">
-        <v>48.66</v>
+        <v>48.39</v>
       </c>
       <c r="P97" s="15">
-        <v>15.344614999999999</v>
+        <v>15.566153999999999</v>
       </c>
       <c r="Q97" s="16">
         <v>1</v>
       </c>
       <c r="R97" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S97" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A98" s="10"/>
       <c r="B98" s="11"/>
       <c r="C98" s="12" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="D98" s="12">
         <v>1</v>
@@ -6317,23 +6341,23 @@
         <v>48.21</v>
       </c>
       <c r="P98" s="15">
-        <v>15.824615</v>
+        <v>15.16</v>
       </c>
       <c r="Q98" s="16">
         <v>1</v>
       </c>
       <c r="R98" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S98" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A99" s="10"/>
       <c r="B99" s="11"/>
       <c r="C99" s="12" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D99" s="12">
         <v>1</v>
@@ -6365,26 +6389,26 @@
       <c r="M99" s="14"/>
       <c r="N99" s="14"/>
       <c r="O99" s="15">
-        <v>48.12</v>
+        <v>48.75</v>
       </c>
       <c r="P99" s="15">
-        <v>15.787692</v>
+        <v>15.344614999999999</v>
       </c>
       <c r="Q99" s="16">
         <v>1</v>
       </c>
       <c r="R99" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S99" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
       <c r="B100" s="11"/>
       <c r="C100" s="12" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="D100" s="12">
         <v>1</v>
@@ -6416,26 +6440,26 @@
       <c r="M100" s="14"/>
       <c r="N100" s="14"/>
       <c r="O100" s="15">
-        <v>48.3</v>
+        <v>48.48</v>
       </c>
       <c r="P100" s="15">
-        <v>15.307691999999999</v>
+        <v>14.901538</v>
       </c>
       <c r="Q100" s="16">
         <v>1</v>
       </c>
       <c r="R100" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S100" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" s="10"/>
       <c r="B101" s="11"/>
       <c r="C101" s="12" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D101" s="12">
         <v>1</v>
@@ -6467,26 +6491,26 @@
       <c r="M101" s="14"/>
       <c r="N101" s="14"/>
       <c r="O101" s="15">
-        <v>48.66</v>
+        <v>47.94</v>
       </c>
       <c r="P101" s="15">
-        <v>15.676923</v>
+        <v>15.123077</v>
       </c>
       <c r="Q101" s="16">
         <v>1</v>
       </c>
       <c r="R101" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S101" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A102" s="10"/>
       <c r="B102" s="11"/>
       <c r="C102" s="12" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D102" s="12">
         <v>1</v>
@@ -6518,26 +6542,26 @@
       <c r="M102" s="14"/>
       <c r="N102" s="14"/>
       <c r="O102" s="15">
-        <v>48.57</v>
+        <v>48.75</v>
       </c>
       <c r="P102" s="15">
-        <v>15.566153999999999</v>
+        <v>15.196923</v>
       </c>
       <c r="Q102" s="16">
         <v>1</v>
       </c>
       <c r="R102" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S102" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103" s="10"/>
       <c r="B103" s="11"/>
       <c r="C103" s="12" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="D103" s="12">
         <v>1</v>
@@ -6569,26 +6593,26 @@
       <c r="M103" s="14"/>
       <c r="N103" s="14"/>
       <c r="O103" s="15">
-        <v>47.94</v>
+        <v>48.39</v>
       </c>
       <c r="P103" s="15">
-        <v>15.270769</v>
+        <v>15.898462</v>
       </c>
       <c r="Q103" s="16">
         <v>1</v>
       </c>
       <c r="R103" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S103" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
       <c r="B104" s="11"/>
       <c r="C104" s="12" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D104" s="12">
         <v>1</v>
@@ -6620,26 +6644,26 @@
       <c r="M104" s="14"/>
       <c r="N104" s="14"/>
       <c r="O104" s="15">
-        <v>47.94</v>
+        <v>48.75</v>
       </c>
       <c r="P104" s="15">
-        <v>15.418462</v>
+        <v>15.233846</v>
       </c>
       <c r="Q104" s="16">
         <v>1</v>
       </c>
       <c r="R104" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S104" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105" s="10"/>
       <c r="B105" s="11"/>
       <c r="C105" s="12" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D105" s="12">
         <v>1</v>
@@ -6671,26 +6695,26 @@
       <c r="M105" s="14"/>
       <c r="N105" s="14"/>
       <c r="O105" s="15">
-        <v>48.21</v>
+        <v>48.66</v>
       </c>
       <c r="P105" s="15">
-        <v>15.270769</v>
+        <v>15.344614999999999</v>
       </c>
       <c r="Q105" s="16">
         <v>1</v>
       </c>
       <c r="R105" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S105" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
       <c r="B106" s="11"/>
       <c r="C106" s="12" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D106" s="12">
         <v>1</v>
@@ -6722,26 +6746,26 @@
       <c r="M106" s="14"/>
       <c r="N106" s="14"/>
       <c r="O106" s="15">
-        <v>48.03</v>
+        <v>48.21</v>
       </c>
       <c r="P106" s="15">
-        <v>16.12</v>
+        <v>15.824615</v>
       </c>
       <c r="Q106" s="16">
         <v>1</v>
       </c>
       <c r="R106" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S106" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A107" s="10"/>
       <c r="B107" s="11"/>
       <c r="C107" s="12" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D107" s="12">
         <v>1</v>
@@ -6776,23 +6800,23 @@
         <v>48.12</v>
       </c>
       <c r="P107" s="15">
-        <v>15.012308000000001</v>
+        <v>15.787692</v>
       </c>
       <c r="Q107" s="16">
         <v>1</v>
       </c>
       <c r="R107" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S107" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A108" s="10"/>
       <c r="B108" s="11"/>
       <c r="C108" s="12" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="D108" s="12">
         <v>1</v>
@@ -6824,26 +6848,26 @@
       <c r="M108" s="14"/>
       <c r="N108" s="14"/>
       <c r="O108" s="15">
-        <v>48.57</v>
+        <v>48.3</v>
       </c>
       <c r="P108" s="15">
-        <v>15.787692</v>
+        <v>15.307691999999999</v>
       </c>
       <c r="Q108" s="16">
         <v>1</v>
       </c>
       <c r="R108" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S108" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A109" s="10"/>
       <c r="B109" s="11"/>
       <c r="C109" s="12" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D109" s="12">
         <v>1</v>
@@ -6875,26 +6899,26 @@
       <c r="M109" s="14"/>
       <c r="N109" s="14"/>
       <c r="O109" s="15">
-        <v>48.48</v>
+        <v>48.66</v>
       </c>
       <c r="P109" s="15">
-        <v>14.938461999999999</v>
+        <v>15.676923</v>
       </c>
       <c r="Q109" s="16">
         <v>1</v>
       </c>
       <c r="R109" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S109" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A110" s="10"/>
       <c r="B110" s="11"/>
       <c r="C110" s="12" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D110" s="12">
         <v>1</v>
@@ -6926,26 +6950,26 @@
       <c r="M110" s="14"/>
       <c r="N110" s="14"/>
       <c r="O110" s="15">
-        <v>48.48</v>
+        <v>48.57</v>
       </c>
       <c r="P110" s="15">
-        <v>15.418462</v>
+        <v>15.566153999999999</v>
       </c>
       <c r="Q110" s="16">
         <v>1</v>
       </c>
       <c r="R110" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S110" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A111" s="10"/>
       <c r="B111" s="11"/>
       <c r="C111" s="12" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D111" s="12">
         <v>1</v>
@@ -6977,26 +7001,26 @@
       <c r="M111" s="14"/>
       <c r="N111" s="14"/>
       <c r="O111" s="15">
-        <v>48.39</v>
+        <v>47.94</v>
       </c>
       <c r="P111" s="15">
-        <v>15.64</v>
+        <v>15.270769</v>
       </c>
       <c r="Q111" s="16">
         <v>1</v>
       </c>
       <c r="R111" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S111" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112" s="10"/>
       <c r="B112" s="11"/>
       <c r="C112" s="12" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D112" s="12">
         <v>1</v>
@@ -7028,26 +7052,26 @@
       <c r="M112" s="14"/>
       <c r="N112" s="14"/>
       <c r="O112" s="15">
-        <v>48.39</v>
+        <v>47.94</v>
       </c>
       <c r="P112" s="15">
-        <v>16.046154000000001</v>
+        <v>15.418462</v>
       </c>
       <c r="Q112" s="16">
         <v>1</v>
       </c>
       <c r="R112" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S112" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A113" s="10"/>
       <c r="B113" s="11"/>
       <c r="C113" s="12" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D113" s="12">
         <v>1</v>
@@ -7079,7 +7103,7 @@
       <c r="M113" s="14"/>
       <c r="N113" s="14"/>
       <c r="O113" s="15">
-        <v>48.12</v>
+        <v>48.21</v>
       </c>
       <c r="P113" s="15">
         <v>15.270769</v>
@@ -7088,17 +7112,17 @@
         <v>1</v>
       </c>
       <c r="R113" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S113" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A114" s="10"/>
       <c r="B114" s="11"/>
       <c r="C114" s="12" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="D114" s="12">
         <v>1</v>
@@ -7130,26 +7154,26 @@
       <c r="M114" s="14"/>
       <c r="N114" s="14"/>
       <c r="O114" s="15">
-        <v>48.48</v>
+        <v>48.03</v>
       </c>
       <c r="P114" s="15">
-        <v>14.753845999999999</v>
+        <v>16.12</v>
       </c>
       <c r="Q114" s="16">
         <v>1</v>
       </c>
       <c r="R114" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S114" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A115" s="10"/>
       <c r="B115" s="11"/>
       <c r="C115" s="12" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D115" s="12">
         <v>1</v>
@@ -7181,26 +7205,26 @@
       <c r="M115" s="14"/>
       <c r="N115" s="14"/>
       <c r="O115" s="15">
-        <v>48.39</v>
+        <v>48.12</v>
       </c>
       <c r="P115" s="15">
-        <v>15.455385</v>
+        <v>15.012308000000001</v>
       </c>
       <c r="Q115" s="16">
         <v>1</v>
       </c>
       <c r="R115" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S115" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A116" s="10"/>
       <c r="B116" s="11"/>
       <c r="C116" s="12" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="D116" s="12">
         <v>1</v>
@@ -7232,26 +7256,26 @@
       <c r="M116" s="14"/>
       <c r="N116" s="14"/>
       <c r="O116" s="15">
-        <v>48.39</v>
+        <v>48.57</v>
       </c>
       <c r="P116" s="15">
-        <v>14.790768999999999</v>
+        <v>15.787692</v>
       </c>
       <c r="Q116" s="16">
         <v>1</v>
       </c>
       <c r="R116" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S116" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A117" s="10"/>
       <c r="B117" s="11"/>
       <c r="C117" s="12" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D117" s="12">
         <v>1</v>
@@ -7283,26 +7307,26 @@
       <c r="M117" s="14"/>
       <c r="N117" s="14"/>
       <c r="O117" s="15">
-        <v>48.21</v>
+        <v>48.48</v>
       </c>
       <c r="P117" s="15">
-        <v>14.975384999999999</v>
+        <v>14.938461999999999</v>
       </c>
       <c r="Q117" s="16">
         <v>1</v>
       </c>
       <c r="R117" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S117" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A118" s="10"/>
       <c r="B118" s="11"/>
       <c r="C118" s="12" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D118" s="12">
         <v>1</v>
@@ -7334,26 +7358,26 @@
       <c r="M118" s="14"/>
       <c r="N118" s="14"/>
       <c r="O118" s="15">
-        <v>48.3</v>
+        <v>48.48</v>
       </c>
       <c r="P118" s="15">
-        <v>15.233846</v>
+        <v>15.418462</v>
       </c>
       <c r="Q118" s="16">
         <v>1</v>
       </c>
       <c r="R118" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S118" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A119" s="10"/>
       <c r="B119" s="11"/>
       <c r="C119" s="12" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D119" s="12">
         <v>1</v>
@@ -7385,26 +7409,26 @@
       <c r="M119" s="14"/>
       <c r="N119" s="14"/>
       <c r="O119" s="15">
-        <v>48.48</v>
+        <v>48.39</v>
       </c>
       <c r="P119" s="15">
-        <v>14.716923</v>
+        <v>15.64</v>
       </c>
       <c r="Q119" s="16">
         <v>1</v>
       </c>
       <c r="R119" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S119" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A120" s="10"/>
       <c r="B120" s="11"/>
       <c r="C120" s="12" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D120" s="12">
         <v>1</v>
@@ -7439,23 +7463,23 @@
         <v>48.39</v>
       </c>
       <c r="P120" s="15">
-        <v>15.935385</v>
+        <v>16.046154000000001</v>
       </c>
       <c r="Q120" s="16">
         <v>1</v>
       </c>
       <c r="R120" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S120" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A121" s="10"/>
       <c r="B121" s="11"/>
       <c r="C121" s="12" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D121" s="12">
         <v>1</v>
@@ -7487,26 +7511,26 @@
       <c r="M121" s="14"/>
       <c r="N121" s="14"/>
       <c r="O121" s="15">
-        <v>48.48</v>
+        <v>48.12</v>
       </c>
       <c r="P121" s="15">
-        <v>14.827692000000001</v>
+        <v>15.270769</v>
       </c>
       <c r="Q121" s="16">
         <v>1</v>
       </c>
       <c r="R121" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S121" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A122" s="10"/>
       <c r="B122" s="11"/>
       <c r="C122" s="12" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="D122" s="12">
         <v>1</v>
@@ -7538,26 +7562,26 @@
       <c r="M122" s="14"/>
       <c r="N122" s="14"/>
       <c r="O122" s="15">
-        <v>48.39</v>
+        <v>48.48</v>
       </c>
       <c r="P122" s="15">
-        <v>16.009231</v>
+        <v>14.753845999999999</v>
       </c>
       <c r="Q122" s="16">
         <v>1</v>
       </c>
       <c r="R122" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S122" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A123" s="10"/>
       <c r="B123" s="11"/>
       <c r="C123" s="12" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D123" s="12">
         <v>1</v>
@@ -7589,26 +7613,26 @@
       <c r="M123" s="14"/>
       <c r="N123" s="14"/>
       <c r="O123" s="15">
-        <v>48.48</v>
+        <v>48.39</v>
       </c>
       <c r="P123" s="15">
-        <v>14.68</v>
+        <v>15.455385</v>
       </c>
       <c r="Q123" s="16">
         <v>1</v>
       </c>
       <c r="R123" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S123" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A124" s="10"/>
       <c r="B124" s="11"/>
       <c r="C124" s="12" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D124" s="12">
         <v>1</v>
@@ -7640,26 +7664,26 @@
       <c r="M124" s="14"/>
       <c r="N124" s="14"/>
       <c r="O124" s="15">
-        <v>48.48</v>
+        <v>48.39</v>
       </c>
       <c r="P124" s="15">
-        <v>15.787692</v>
+        <v>14.790768999999999</v>
       </c>
       <c r="Q124" s="16">
         <v>1</v>
       </c>
       <c r="R124" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S124" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A125" s="10"/>
       <c r="B125" s="11"/>
       <c r="C125" s="12" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="D125" s="12">
         <v>1</v>
@@ -7691,26 +7715,26 @@
       <c r="M125" s="14"/>
       <c r="N125" s="14"/>
       <c r="O125" s="15">
-        <v>48.39</v>
+        <v>48.21</v>
       </c>
       <c r="P125" s="15">
-        <v>15.012308000000001</v>
+        <v>14.975384999999999</v>
       </c>
       <c r="Q125" s="16">
         <v>1</v>
       </c>
       <c r="R125" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S125" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A126" s="10"/>
       <c r="B126" s="11"/>
       <c r="C126" s="12" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="D126" s="12">
         <v>1</v>
@@ -7742,26 +7766,26 @@
       <c r="M126" s="14"/>
       <c r="N126" s="14"/>
       <c r="O126" s="15">
-        <v>48.48</v>
+        <v>48.3</v>
       </c>
       <c r="P126" s="15">
-        <v>15.64</v>
+        <v>15.233846</v>
       </c>
       <c r="Q126" s="16">
         <v>1</v>
       </c>
       <c r="R126" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S126" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A127" s="10"/>
       <c r="B127" s="11"/>
       <c r="C127" s="12" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D127" s="12">
         <v>1</v>
@@ -7793,26 +7817,26 @@
       <c r="M127" s="14"/>
       <c r="N127" s="14"/>
       <c r="O127" s="15">
-        <v>48.03</v>
+        <v>48.48</v>
       </c>
       <c r="P127" s="15">
-        <v>15.418462</v>
+        <v>14.716923</v>
       </c>
       <c r="Q127" s="16">
         <v>1</v>
       </c>
       <c r="R127" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S127" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A128" s="10"/>
       <c r="B128" s="11"/>
       <c r="C128" s="12" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D128" s="12">
         <v>1</v>
@@ -7844,26 +7868,26 @@
       <c r="M128" s="14"/>
       <c r="N128" s="14"/>
       <c r="O128" s="15">
-        <v>48.03</v>
+        <v>48.39</v>
       </c>
       <c r="P128" s="15">
-        <v>15.381538000000001</v>
+        <v>15.935385</v>
       </c>
       <c r="Q128" s="16">
         <v>1</v>
       </c>
       <c r="R128" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S128" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A129" s="10"/>
       <c r="B129" s="11"/>
       <c r="C129" s="12" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D129" s="12">
         <v>1</v>
@@ -7895,26 +7919,26 @@
       <c r="M129" s="14"/>
       <c r="N129" s="14"/>
       <c r="O129" s="15">
-        <v>48.21</v>
+        <v>48.48</v>
       </c>
       <c r="P129" s="15">
-        <v>15.307691999999999</v>
+        <v>14.827692000000001</v>
       </c>
       <c r="Q129" s="16">
         <v>1</v>
       </c>
       <c r="R129" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S129" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A130" s="10"/>
       <c r="B130" s="11"/>
       <c r="C130" s="12" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="D130" s="12">
         <v>1</v>
@@ -7946,26 +7970,26 @@
       <c r="M130" s="14"/>
       <c r="N130" s="14"/>
       <c r="O130" s="15">
-        <v>48.12</v>
+        <v>48.39</v>
       </c>
       <c r="P130" s="15">
-        <v>15.344614999999999</v>
+        <v>16.009231</v>
       </c>
       <c r="Q130" s="16">
         <v>1</v>
       </c>
       <c r="R130" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S130" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A131" s="10"/>
       <c r="B131" s="11"/>
       <c r="C131" s="12" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D131" s="12">
         <v>1</v>
@@ -7997,26 +8021,26 @@
       <c r="M131" s="14"/>
       <c r="N131" s="14"/>
       <c r="O131" s="15">
-        <v>48.39</v>
+        <v>48.48</v>
       </c>
       <c r="P131" s="15">
-        <v>15.492308</v>
+        <v>14.68</v>
       </c>
       <c r="Q131" s="16">
         <v>1</v>
       </c>
       <c r="R131" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S131" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A132" s="10"/>
       <c r="B132" s="11"/>
       <c r="C132" s="12" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D132" s="12">
         <v>1</v>
@@ -8048,26 +8072,26 @@
       <c r="M132" s="14"/>
       <c r="N132" s="14"/>
       <c r="O132" s="15">
-        <v>47.85</v>
+        <v>48.48</v>
       </c>
       <c r="P132" s="15">
-        <v>15.196923</v>
+        <v>15.787692</v>
       </c>
       <c r="Q132" s="16">
         <v>1</v>
       </c>
       <c r="R132" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S132" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A133" s="10"/>
       <c r="B133" s="11"/>
       <c r="C133" s="12" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D133" s="12">
         <v>1</v>
@@ -8099,26 +8123,26 @@
       <c r="M133" s="14"/>
       <c r="N133" s="14"/>
       <c r="O133" s="15">
-        <v>48.3</v>
+        <v>48.39</v>
       </c>
       <c r="P133" s="15">
-        <v>14.938461999999999</v>
+        <v>15.012308000000001</v>
       </c>
       <c r="Q133" s="16">
         <v>1</v>
       </c>
       <c r="R133" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S133" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A134" s="10"/>
       <c r="B134" s="11"/>
       <c r="C134" s="12" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D134" s="12">
         <v>1</v>
@@ -8150,26 +8174,26 @@
       <c r="M134" s="14"/>
       <c r="N134" s="14"/>
       <c r="O134" s="15">
-        <v>47.94</v>
+        <v>48.48</v>
       </c>
       <c r="P134" s="15">
-        <v>15.455385</v>
+        <v>15.64</v>
       </c>
       <c r="Q134" s="16">
         <v>1</v>
       </c>
       <c r="R134" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S134" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A135" s="10"/>
       <c r="B135" s="11"/>
       <c r="C135" s="12" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D135" s="12">
         <v>1</v>
@@ -8201,26 +8225,26 @@
       <c r="M135" s="14"/>
       <c r="N135" s="14"/>
       <c r="O135" s="15">
-        <v>48.21</v>
+        <v>48.03</v>
       </c>
       <c r="P135" s="15">
-        <v>15.123077</v>
+        <v>15.418462</v>
       </c>
       <c r="Q135" s="16">
         <v>1</v>
       </c>
       <c r="R135" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S135" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A136" s="10"/>
       <c r="B136" s="11"/>
       <c r="C136" s="12" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D136" s="12">
         <v>1</v>
@@ -8252,26 +8276,26 @@
       <c r="M136" s="14"/>
       <c r="N136" s="14"/>
       <c r="O136" s="15">
-        <v>48.21</v>
+        <v>48.03</v>
       </c>
       <c r="P136" s="15">
-        <v>15.344614999999999</v>
+        <v>15.381538000000001</v>
       </c>
       <c r="Q136" s="16">
         <v>1</v>
       </c>
       <c r="R136" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S136" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A137" s="10"/>
       <c r="B137" s="11"/>
       <c r="C137" s="12" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D137" s="12">
         <v>1</v>
@@ -8303,26 +8327,26 @@
       <c r="M137" s="14"/>
       <c r="N137" s="14"/>
       <c r="O137" s="15">
-        <v>48.3</v>
+        <v>48.21</v>
       </c>
       <c r="P137" s="15">
-        <v>15.455385</v>
+        <v>15.307691999999999</v>
       </c>
       <c r="Q137" s="16">
         <v>1</v>
       </c>
       <c r="R137" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S137" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A138" s="10"/>
       <c r="B138" s="11"/>
       <c r="C138" s="12" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D138" s="12">
         <v>1</v>
@@ -8357,23 +8381,23 @@
         <v>48.12</v>
       </c>
       <c r="P138" s="15">
-        <v>14.753845999999999</v>
+        <v>15.344614999999999</v>
       </c>
       <c r="Q138" s="16">
         <v>1</v>
       </c>
       <c r="R138" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S138" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A139" s="10"/>
       <c r="B139" s="11"/>
       <c r="C139" s="12" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="D139" s="12">
         <v>1</v>
@@ -8405,26 +8429,26 @@
       <c r="M139" s="14"/>
       <c r="N139" s="14"/>
       <c r="O139" s="15">
-        <v>48.3</v>
+        <v>48.39</v>
       </c>
       <c r="P139" s="15">
-        <v>14.716923</v>
+        <v>15.492308</v>
       </c>
       <c r="Q139" s="16">
         <v>1</v>
       </c>
       <c r="R139" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S139" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A140" s="10"/>
       <c r="B140" s="11"/>
       <c r="C140" s="12" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D140" s="12">
         <v>1</v>
@@ -8456,26 +8480,26 @@
       <c r="M140" s="14"/>
       <c r="N140" s="14"/>
       <c r="O140" s="15">
-        <v>48.03</v>
+        <v>47.85</v>
       </c>
       <c r="P140" s="15">
-        <v>15.566153999999999</v>
+        <v>15.196923</v>
       </c>
       <c r="Q140" s="16">
         <v>1</v>
       </c>
       <c r="R140" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S140" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A141" s="10"/>
       <c r="B141" s="11"/>
       <c r="C141" s="12" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D141" s="12">
         <v>1</v>
@@ -8507,26 +8531,26 @@
       <c r="M141" s="14"/>
       <c r="N141" s="14"/>
       <c r="O141" s="15">
-        <v>48.03</v>
+        <v>48.3</v>
       </c>
       <c r="P141" s="15">
-        <v>15.750769</v>
+        <v>14.938461999999999</v>
       </c>
       <c r="Q141" s="16">
         <v>1</v>
       </c>
       <c r="R141" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S141" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A142" s="10"/>
       <c r="B142" s="11"/>
       <c r="C142" s="12" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="D142" s="12">
         <v>1</v>
@@ -8558,26 +8582,26 @@
       <c r="M142" s="14"/>
       <c r="N142" s="14"/>
       <c r="O142" s="15">
-        <v>48.12</v>
+        <v>47.94</v>
       </c>
       <c r="P142" s="15">
-        <v>15.492308</v>
+        <v>15.455385</v>
       </c>
       <c r="Q142" s="16">
         <v>1</v>
       </c>
       <c r="R142" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S142" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A143" s="10"/>
       <c r="B143" s="11"/>
       <c r="C143" s="12" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D143" s="12">
         <v>1</v>
@@ -8609,26 +8633,26 @@
       <c r="M143" s="14"/>
       <c r="N143" s="14"/>
       <c r="O143" s="15">
-        <v>48.03</v>
+        <v>48.21</v>
       </c>
       <c r="P143" s="15">
-        <v>15.086154000000001</v>
+        <v>15.123077</v>
       </c>
       <c r="Q143" s="16">
         <v>1</v>
       </c>
       <c r="R143" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S143" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A144" s="10"/>
       <c r="B144" s="11"/>
       <c r="C144" s="12" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="D144" s="12">
         <v>1</v>
@@ -8660,26 +8684,26 @@
       <c r="M144" s="14"/>
       <c r="N144" s="14"/>
       <c r="O144" s="15">
-        <v>48.3</v>
+        <v>48.21</v>
       </c>
       <c r="P144" s="15">
-        <v>14.864615000000001</v>
+        <v>15.344614999999999</v>
       </c>
       <c r="Q144" s="16">
         <v>1</v>
       </c>
       <c r="R144" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S144" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
       <c r="B145" s="11"/>
       <c r="C145" s="12" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D145" s="12">
         <v>1</v>
@@ -8711,26 +8735,26 @@
       <c r="M145" s="14"/>
       <c r="N145" s="14"/>
       <c r="O145" s="15">
-        <v>47.94</v>
+        <v>48.3</v>
       </c>
       <c r="P145" s="15">
-        <v>15.307691999999999</v>
+        <v>15.455385</v>
       </c>
       <c r="Q145" s="16">
         <v>1</v>
       </c>
       <c r="R145" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S145" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
       <c r="B146" s="11"/>
       <c r="C146" s="12" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D146" s="12">
         <v>1</v>
@@ -8762,26 +8786,26 @@
       <c r="M146" s="14"/>
       <c r="N146" s="14"/>
       <c r="O146" s="15">
-        <v>48.39</v>
+        <v>48.12</v>
       </c>
       <c r="P146" s="15">
-        <v>15.861537999999999</v>
+        <v>14.753845999999999</v>
       </c>
       <c r="Q146" s="16">
         <v>1</v>
       </c>
       <c r="R146" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S146" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
       <c r="B147" s="11"/>
       <c r="C147" s="12" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D147" s="12">
         <v>1</v>
@@ -8813,26 +8837,26 @@
       <c r="M147" s="14"/>
       <c r="N147" s="14"/>
       <c r="O147" s="15">
-        <v>48.21</v>
+        <v>48.3</v>
       </c>
       <c r="P147" s="15">
-        <v>15.898462</v>
+        <v>14.716923</v>
       </c>
       <c r="Q147" s="16">
         <v>1</v>
       </c>
       <c r="R147" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S147" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A148" s="10"/>
       <c r="B148" s="11"/>
       <c r="C148" s="12" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="D148" s="12">
         <v>1</v>
@@ -8864,26 +8888,26 @@
       <c r="M148" s="14"/>
       <c r="N148" s="14"/>
       <c r="O148" s="15">
-        <v>48.48</v>
+        <v>48.03</v>
       </c>
       <c r="P148" s="15">
-        <v>15.824615</v>
+        <v>15.566153999999999</v>
       </c>
       <c r="Q148" s="16">
         <v>1</v>
       </c>
       <c r="R148" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S148" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A149" s="10"/>
       <c r="B149" s="11"/>
       <c r="C149" s="12" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="D149" s="12">
         <v>1</v>
@@ -8915,7 +8939,7 @@
       <c r="M149" s="14"/>
       <c r="N149" s="14"/>
       <c r="O149" s="15">
-        <v>48.48</v>
+        <v>48.03</v>
       </c>
       <c r="P149" s="15">
         <v>15.750769</v>
@@ -8924,17 +8948,17 @@
         <v>1</v>
       </c>
       <c r="R149" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S149" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A150" s="10"/>
       <c r="B150" s="11"/>
       <c r="C150" s="12" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="D150" s="12">
         <v>1</v>
@@ -8966,26 +8990,26 @@
       <c r="M150" s="14"/>
       <c r="N150" s="14"/>
       <c r="O150" s="15">
-        <v>48.48</v>
+        <v>48.12</v>
       </c>
       <c r="P150" s="15">
-        <v>15.196923</v>
+        <v>15.492308</v>
       </c>
       <c r="Q150" s="16">
         <v>1</v>
       </c>
       <c r="R150" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S150" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A151" s="10"/>
       <c r="B151" s="11"/>
       <c r="C151" s="12" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D151" s="12">
         <v>1</v>
@@ -9017,26 +9041,26 @@
       <c r="M151" s="14"/>
       <c r="N151" s="14"/>
       <c r="O151" s="15">
-        <v>48.3</v>
+        <v>48.03</v>
       </c>
       <c r="P151" s="15">
-        <v>15.344614999999999</v>
+        <v>15.086154000000001</v>
       </c>
       <c r="Q151" s="16">
         <v>1</v>
       </c>
       <c r="R151" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S151" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A152" s="10"/>
       <c r="B152" s="11"/>
       <c r="C152" s="12" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D152" s="12">
         <v>1</v>
@@ -9068,26 +9092,26 @@
       <c r="M152" s="14"/>
       <c r="N152" s="14"/>
       <c r="O152" s="15">
-        <v>48.12</v>
+        <v>48.3</v>
       </c>
       <c r="P152" s="15">
-        <v>14.975384999999999</v>
+        <v>14.864615000000001</v>
       </c>
       <c r="Q152" s="16">
         <v>1</v>
       </c>
       <c r="R152" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S152" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A153" s="10"/>
       <c r="B153" s="11"/>
       <c r="C153" s="12" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D153" s="12">
         <v>1</v>
@@ -9119,26 +9143,26 @@
       <c r="M153" s="14"/>
       <c r="N153" s="14"/>
       <c r="O153" s="15">
-        <v>48.48</v>
+        <v>47.94</v>
       </c>
       <c r="P153" s="15">
-        <v>15.049231000000001</v>
+        <v>15.307691999999999</v>
       </c>
       <c r="Q153" s="16">
         <v>1</v>
       </c>
       <c r="R153" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S153" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A154" s="10"/>
       <c r="B154" s="11"/>
       <c r="C154" s="12" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="D154" s="12">
         <v>1</v>
@@ -9173,23 +9197,23 @@
         <v>48.39</v>
       </c>
       <c r="P154" s="15">
-        <v>15.344614999999999</v>
+        <v>15.861537999999999</v>
       </c>
       <c r="Q154" s="16">
         <v>1</v>
       </c>
       <c r="R154" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S154" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A155" s="10"/>
       <c r="B155" s="11"/>
       <c r="C155" s="12" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D155" s="12">
         <v>1</v>
@@ -9221,26 +9245,26 @@
       <c r="M155" s="14"/>
       <c r="N155" s="14"/>
       <c r="O155" s="15">
-        <v>48.66</v>
+        <v>48.21</v>
       </c>
       <c r="P155" s="15">
-        <v>15.455385</v>
+        <v>15.898462</v>
       </c>
       <c r="Q155" s="16">
         <v>1</v>
       </c>
       <c r="R155" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S155" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A156" s="10"/>
       <c r="B156" s="11"/>
       <c r="C156" s="12" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D156" s="12">
         <v>1</v>
@@ -9272,26 +9296,26 @@
       <c r="M156" s="14"/>
       <c r="N156" s="14"/>
       <c r="O156" s="15">
-        <v>48.39</v>
+        <v>48.48</v>
       </c>
       <c r="P156" s="15">
-        <v>15.233846</v>
+        <v>15.824615</v>
       </c>
       <c r="Q156" s="16">
         <v>1</v>
       </c>
       <c r="R156" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S156" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A157" s="10"/>
       <c r="B157" s="11"/>
       <c r="C157" s="12" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D157" s="12">
         <v>1</v>
@@ -9323,26 +9347,26 @@
       <c r="M157" s="14"/>
       <c r="N157" s="14"/>
       <c r="O157" s="15">
-        <v>48.66</v>
+        <v>48.48</v>
       </c>
       <c r="P157" s="15">
-        <v>15.233846</v>
+        <v>15.750769</v>
       </c>
       <c r="Q157" s="16">
         <v>1</v>
       </c>
       <c r="R157" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S157" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A158" s="10"/>
       <c r="B158" s="11"/>
       <c r="C158" s="12" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D158" s="12">
         <v>1</v>
@@ -9377,23 +9401,23 @@
         <v>48.48</v>
       </c>
       <c r="P158" s="15">
-        <v>15.529230999999999</v>
+        <v>15.196923</v>
       </c>
       <c r="Q158" s="16">
         <v>1</v>
       </c>
       <c r="R158" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S158" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A159" s="10"/>
       <c r="B159" s="11"/>
       <c r="C159" s="12" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D159" s="12">
         <v>1</v>
@@ -9425,26 +9449,26 @@
       <c r="M159" s="14"/>
       <c r="N159" s="14"/>
       <c r="O159" s="15">
-        <v>48.75</v>
+        <v>48.3</v>
       </c>
       <c r="P159" s="15">
-        <v>15.16</v>
+        <v>15.344614999999999</v>
       </c>
       <c r="Q159" s="16">
         <v>1</v>
       </c>
       <c r="R159" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S159" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A160" s="10"/>
       <c r="B160" s="11"/>
       <c r="C160" s="12" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D160" s="12">
         <v>1</v>
@@ -9476,26 +9500,26 @@
       <c r="M160" s="14"/>
       <c r="N160" s="14"/>
       <c r="O160" s="15">
-        <v>48.39</v>
+        <v>48.12</v>
       </c>
       <c r="P160" s="15">
-        <v>15.16</v>
+        <v>14.975384999999999</v>
       </c>
       <c r="Q160" s="16">
         <v>1</v>
       </c>
       <c r="R160" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S160" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A161" s="10"/>
       <c r="B161" s="11"/>
       <c r="C161" s="12" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D161" s="12">
         <v>1</v>
@@ -9527,26 +9551,26 @@
       <c r="M161" s="14"/>
       <c r="N161" s="14"/>
       <c r="O161" s="15">
-        <v>48.12</v>
+        <v>48.48</v>
       </c>
       <c r="P161" s="15">
-        <v>15.123077</v>
+        <v>15.049231000000001</v>
       </c>
       <c r="Q161" s="16">
         <v>1</v>
       </c>
       <c r="R161" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S161" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A162" s="10"/>
       <c r="B162" s="11"/>
       <c r="C162" s="12" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D162" s="12">
         <v>1</v>
@@ -9578,26 +9602,26 @@
       <c r="M162" s="14"/>
       <c r="N162" s="14"/>
       <c r="O162" s="15">
-        <v>48.48</v>
+        <v>48.39</v>
       </c>
       <c r="P162" s="15">
-        <v>16.083076999999999</v>
+        <v>15.344614999999999</v>
       </c>
       <c r="Q162" s="16">
         <v>1</v>
       </c>
       <c r="R162" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S162" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A163" s="10"/>
       <c r="B163" s="11"/>
       <c r="C163" s="12" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="D163" s="12">
         <v>1</v>
@@ -9629,26 +9653,26 @@
       <c r="M163" s="14"/>
       <c r="N163" s="14"/>
       <c r="O163" s="15">
-        <v>48.12</v>
+        <v>48.66</v>
       </c>
       <c r="P163" s="15">
-        <v>15.676923</v>
+        <v>15.455385</v>
       </c>
       <c r="Q163" s="16">
         <v>1</v>
       </c>
       <c r="R163" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S163" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A164" s="10"/>
       <c r="B164" s="11"/>
       <c r="C164" s="12" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D164" s="12">
         <v>1</v>
@@ -9680,26 +9704,26 @@
       <c r="M164" s="14"/>
       <c r="N164" s="14"/>
       <c r="O164" s="15">
-        <v>48.12</v>
+        <v>48.39</v>
       </c>
       <c r="P164" s="15">
-        <v>15.603077000000001</v>
+        <v>15.233846</v>
       </c>
       <c r="Q164" s="16">
         <v>1</v>
       </c>
       <c r="R164" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S164" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A165" s="10"/>
       <c r="B165" s="11"/>
       <c r="C165" s="12" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="D165" s="12">
         <v>1</v>
@@ -9731,26 +9755,26 @@
       <c r="M165" s="14"/>
       <c r="N165" s="14"/>
       <c r="O165" s="15">
-        <v>48.03</v>
+        <v>48.66</v>
       </c>
       <c r="P165" s="15">
-        <v>14.901538</v>
+        <v>15.233846</v>
       </c>
       <c r="Q165" s="16">
         <v>1</v>
       </c>
       <c r="R165" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S165" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A166" s="10"/>
       <c r="B166" s="11"/>
       <c r="C166" s="12" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="D166" s="12">
         <v>1</v>
@@ -9785,23 +9809,23 @@
         <v>48.48</v>
       </c>
       <c r="P166" s="15">
-        <v>15.455385</v>
+        <v>15.529230999999999</v>
       </c>
       <c r="Q166" s="16">
         <v>1</v>
       </c>
       <c r="R166" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S166" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A167" s="10"/>
       <c r="B167" s="11"/>
       <c r="C167" s="12" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="D167" s="12">
         <v>1</v>
@@ -9833,26 +9857,26 @@
       <c r="M167" s="14"/>
       <c r="N167" s="14"/>
       <c r="O167" s="15">
-        <v>48.12</v>
+        <v>48.75</v>
       </c>
       <c r="P167" s="15">
-        <v>14.901538</v>
+        <v>15.16</v>
       </c>
       <c r="Q167" s="16">
         <v>1</v>
       </c>
       <c r="R167" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S167" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A168" s="10"/>
       <c r="B168" s="11"/>
       <c r="C168" s="12" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D168" s="12">
         <v>1</v>
@@ -9884,26 +9908,26 @@
       <c r="M168" s="14"/>
       <c r="N168" s="14"/>
       <c r="O168" s="15">
-        <v>48.21</v>
+        <v>48.39</v>
       </c>
       <c r="P168" s="15">
-        <v>14.864615000000001</v>
+        <v>15.16</v>
       </c>
       <c r="Q168" s="16">
         <v>1</v>
       </c>
       <c r="R168" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S168" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A169" s="10"/>
       <c r="B169" s="11"/>
       <c r="C169" s="12" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="D169" s="12">
         <v>1</v>
@@ -9935,26 +9959,26 @@
       <c r="M169" s="14"/>
       <c r="N169" s="14"/>
       <c r="O169" s="15">
-        <v>48.48</v>
+        <v>48.12</v>
       </c>
       <c r="P169" s="15">
-        <v>14.864615000000001</v>
+        <v>15.123077</v>
       </c>
       <c r="Q169" s="16">
         <v>1</v>
       </c>
       <c r="R169" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S169" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A170" s="10"/>
       <c r="B170" s="11"/>
       <c r="C170" s="12" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="D170" s="12">
         <v>1</v>
@@ -9986,26 +10010,26 @@
       <c r="M170" s="14"/>
       <c r="N170" s="14"/>
       <c r="O170" s="15">
-        <v>48.75</v>
+        <v>48.48</v>
       </c>
       <c r="P170" s="15">
-        <v>15.381538000000001</v>
+        <v>16.083076999999999</v>
       </c>
       <c r="Q170" s="16">
         <v>1</v>
       </c>
       <c r="R170" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S170" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A171" s="10"/>
       <c r="B171" s="11"/>
       <c r="C171" s="12" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="D171" s="12">
         <v>1</v>
@@ -10037,26 +10061,26 @@
       <c r="M171" s="14"/>
       <c r="N171" s="14"/>
       <c r="O171" s="15">
-        <v>47.85</v>
+        <v>48.12</v>
       </c>
       <c r="P171" s="15">
-        <v>15.270769</v>
+        <v>15.676923</v>
       </c>
       <c r="Q171" s="16">
         <v>1</v>
       </c>
       <c r="R171" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S171" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A172" s="10"/>
       <c r="B172" s="11"/>
       <c r="C172" s="12" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="D172" s="12">
         <v>1</v>
@@ -10091,23 +10115,23 @@
         <v>48.12</v>
       </c>
       <c r="P172" s="15">
-        <v>15.196923</v>
+        <v>15.603077000000001</v>
       </c>
       <c r="Q172" s="16">
         <v>1</v>
       </c>
       <c r="R172" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S172" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A173" s="10"/>
       <c r="B173" s="11"/>
       <c r="C173" s="12" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D173" s="12">
         <v>1</v>
@@ -10139,26 +10163,26 @@
       <c r="M173" s="14"/>
       <c r="N173" s="14"/>
       <c r="O173" s="15">
-        <v>48.3</v>
+        <v>48.03</v>
       </c>
       <c r="P173" s="15">
-        <v>15.16</v>
+        <v>14.901538</v>
       </c>
       <c r="Q173" s="16">
         <v>1</v>
       </c>
       <c r="R173" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S173" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A174" s="10"/>
       <c r="B174" s="11"/>
       <c r="C174" s="12" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D174" s="12">
         <v>1</v>
@@ -10193,23 +10217,23 @@
         <v>48.48</v>
       </c>
       <c r="P174" s="15">
-        <v>16.009231</v>
+        <v>15.455385</v>
       </c>
       <c r="Q174" s="16">
         <v>1</v>
       </c>
       <c r="R174" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S174" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A175" s="10"/>
       <c r="B175" s="11"/>
       <c r="C175" s="12" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D175" s="12">
         <v>1</v>
@@ -10244,23 +10268,23 @@
         <v>48.12</v>
       </c>
       <c r="P175" s="15">
-        <v>15.750769</v>
+        <v>14.901538</v>
       </c>
       <c r="Q175" s="16">
         <v>1</v>
       </c>
       <c r="R175" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S175" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A176" s="10"/>
       <c r="B176" s="11"/>
       <c r="C176" s="12" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="D176" s="12">
         <v>1</v>
@@ -10292,26 +10316,26 @@
       <c r="M176" s="14"/>
       <c r="N176" s="14"/>
       <c r="O176" s="15">
-        <v>48.3</v>
+        <v>48.21</v>
       </c>
       <c r="P176" s="15">
-        <v>15.270769</v>
+        <v>14.864615000000001</v>
       </c>
       <c r="Q176" s="16">
         <v>1</v>
       </c>
       <c r="R176" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S176" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A177" s="10"/>
       <c r="B177" s="11"/>
       <c r="C177" s="12" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="D177" s="12">
         <v>1</v>
@@ -10343,26 +10367,26 @@
       <c r="M177" s="14"/>
       <c r="N177" s="14"/>
       <c r="O177" s="15">
-        <v>48.21</v>
+        <v>48.48</v>
       </c>
       <c r="P177" s="15">
-        <v>15.196923</v>
+        <v>14.864615000000001</v>
       </c>
       <c r="Q177" s="16">
         <v>1</v>
       </c>
       <c r="R177" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S177" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A178" s="10"/>
       <c r="B178" s="11"/>
       <c r="C178" s="12" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="D178" s="12">
         <v>1</v>
@@ -10394,26 +10418,26 @@
       <c r="M178" s="14"/>
       <c r="N178" s="14"/>
       <c r="O178" s="15">
-        <v>48.03</v>
+        <v>48.75</v>
       </c>
       <c r="P178" s="15">
-        <v>16.083076999999999</v>
+        <v>15.381538000000001</v>
       </c>
       <c r="Q178" s="16">
         <v>1</v>
       </c>
       <c r="R178" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S178" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A179" s="10"/>
       <c r="B179" s="11"/>
       <c r="C179" s="12" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="D179" s="12">
         <v>1</v>
@@ -10445,26 +10469,26 @@
       <c r="M179" s="14"/>
       <c r="N179" s="14"/>
       <c r="O179" s="15">
-        <v>48.12</v>
+        <v>47.85</v>
       </c>
       <c r="P179" s="15">
-        <v>15.049231000000001</v>
+        <v>15.270769</v>
       </c>
       <c r="Q179" s="16">
         <v>1</v>
       </c>
       <c r="R179" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S179" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A180" s="10"/>
       <c r="B180" s="11"/>
       <c r="C180" s="12" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="D180" s="12">
         <v>1</v>
@@ -10496,26 +10520,26 @@
       <c r="M180" s="14"/>
       <c r="N180" s="14"/>
       <c r="O180" s="15">
-        <v>48.21</v>
+        <v>48.12</v>
       </c>
       <c r="P180" s="15">
-        <v>14.938461999999999</v>
+        <v>15.196923</v>
       </c>
       <c r="Q180" s="16">
         <v>1</v>
       </c>
       <c r="R180" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S180" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A181" s="10"/>
       <c r="B181" s="11"/>
       <c r="C181" s="12" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D181" s="12">
         <v>1</v>
@@ -10547,26 +10571,26 @@
       <c r="M181" s="14"/>
       <c r="N181" s="14"/>
       <c r="O181" s="15">
-        <v>48.39</v>
+        <v>48.3</v>
       </c>
       <c r="P181" s="15">
-        <v>15.603077000000001</v>
+        <v>15.16</v>
       </c>
       <c r="Q181" s="16">
         <v>1</v>
       </c>
       <c r="R181" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S181" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A182" s="10"/>
       <c r="B182" s="11"/>
       <c r="C182" s="12" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="D182" s="12">
         <v>1</v>
@@ -10598,26 +10622,26 @@
       <c r="M182" s="14"/>
       <c r="N182" s="14"/>
       <c r="O182" s="15">
-        <v>48.39</v>
+        <v>48.48</v>
       </c>
       <c r="P182" s="15">
-        <v>14.827692000000001</v>
+        <v>16.009231</v>
       </c>
       <c r="Q182" s="16">
         <v>1</v>
       </c>
       <c r="R182" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S182" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A183" s="10"/>
       <c r="B183" s="11"/>
       <c r="C183" s="12" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D183" s="12">
         <v>1</v>
@@ -10649,26 +10673,26 @@
       <c r="M183" s="14"/>
       <c r="N183" s="14"/>
       <c r="O183" s="15">
-        <v>48.57</v>
+        <v>48.12</v>
       </c>
       <c r="P183" s="15">
-        <v>14.716923</v>
+        <v>15.750769</v>
       </c>
       <c r="Q183" s="16">
         <v>1</v>
       </c>
       <c r="R183" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S183" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A184" s="10"/>
       <c r="B184" s="11"/>
       <c r="C184" s="12" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="D184" s="12">
         <v>1</v>
@@ -10700,26 +10724,26 @@
       <c r="M184" s="14"/>
       <c r="N184" s="14"/>
       <c r="O184" s="15">
-        <v>48.21</v>
+        <v>48.3</v>
       </c>
       <c r="P184" s="15">
-        <v>15.012308000000001</v>
+        <v>15.270769</v>
       </c>
       <c r="Q184" s="16">
         <v>1</v>
       </c>
       <c r="R184" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S184" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A185" s="10"/>
       <c r="B185" s="11"/>
       <c r="C185" s="12" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D185" s="12">
         <v>1</v>
@@ -10751,26 +10775,26 @@
       <c r="M185" s="14"/>
       <c r="N185" s="14"/>
       <c r="O185" s="15">
-        <v>48.39</v>
+        <v>48.21</v>
       </c>
       <c r="P185" s="15">
-        <v>15.049231000000001</v>
+        <v>15.196923</v>
       </c>
       <c r="Q185" s="16">
         <v>1</v>
       </c>
       <c r="R185" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S185" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A186" s="10"/>
       <c r="B186" s="11"/>
       <c r="C186" s="12" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D186" s="12">
         <v>1</v>
@@ -10802,26 +10826,26 @@
       <c r="M186" s="14"/>
       <c r="N186" s="14"/>
       <c r="O186" s="15">
-        <v>48.48</v>
+        <v>48.03</v>
       </c>
       <c r="P186" s="15">
-        <v>15.935385</v>
+        <v>16.083076999999999</v>
       </c>
       <c r="Q186" s="16">
         <v>1</v>
       </c>
       <c r="R186" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S186" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A187" s="10"/>
       <c r="B187" s="11"/>
       <c r="C187" s="12" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D187" s="12">
         <v>1</v>
@@ -10853,26 +10877,26 @@
       <c r="M187" s="14"/>
       <c r="N187" s="14"/>
       <c r="O187" s="15">
-        <v>48.3</v>
+        <v>48.12</v>
       </c>
       <c r="P187" s="15">
-        <v>14.975384999999999</v>
+        <v>15.049231000000001</v>
       </c>
       <c r="Q187" s="16">
         <v>1</v>
       </c>
       <c r="R187" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S187" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A188" s="10"/>
       <c r="B188" s="11"/>
       <c r="C188" s="12" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D188" s="12">
         <v>1</v>
@@ -10904,26 +10928,26 @@
       <c r="M188" s="14"/>
       <c r="N188" s="14"/>
       <c r="O188" s="15">
-        <v>48.39</v>
+        <v>48.21</v>
       </c>
       <c r="P188" s="15">
-        <v>15.418462</v>
+        <v>14.938461999999999</v>
       </c>
       <c r="Q188" s="16">
         <v>1</v>
       </c>
       <c r="R188" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S188" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A189" s="10"/>
       <c r="B189" s="11"/>
       <c r="C189" s="12" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D189" s="12">
         <v>1</v>
@@ -10955,26 +10979,26 @@
       <c r="M189" s="14"/>
       <c r="N189" s="14"/>
       <c r="O189" s="15">
-        <v>48.3</v>
+        <v>48.39</v>
       </c>
       <c r="P189" s="15">
-        <v>15.012308000000001</v>
+        <v>15.603077000000001</v>
       </c>
       <c r="Q189" s="16">
         <v>1</v>
       </c>
       <c r="R189" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S189" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A190" s="10"/>
       <c r="B190" s="11"/>
       <c r="C190" s="12" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D190" s="12">
         <v>1</v>
@@ -11006,7 +11030,7 @@
       <c r="M190" s="14"/>
       <c r="N190" s="14"/>
       <c r="O190" s="15">
-        <v>48.57</v>
+        <v>48.39</v>
       </c>
       <c r="P190" s="15">
         <v>14.827692000000001</v>
@@ -11015,17 +11039,17 @@
         <v>1</v>
       </c>
       <c r="R190" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S190" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A191" s="10"/>
       <c r="B191" s="11"/>
       <c r="C191" s="12" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D191" s="12">
         <v>1</v>
@@ -11057,26 +11081,26 @@
       <c r="M191" s="14"/>
       <c r="N191" s="14"/>
       <c r="O191" s="15">
-        <v>48.21</v>
+        <v>48.57</v>
       </c>
       <c r="P191" s="15">
-        <v>15.233846</v>
+        <v>14.716923</v>
       </c>
       <c r="Q191" s="16">
         <v>1</v>
       </c>
       <c r="R191" s="17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="S191" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A192" s="10"/>
       <c r="B192" s="11"/>
       <c r="C192" s="12" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D192" s="12">
         <v>1</v>
@@ -11108,18 +11132,426 @@
       <c r="M192" s="14"/>
       <c r="N192" s="14"/>
       <c r="O192" s="15">
+        <v>48.21</v>
+      </c>
+      <c r="P192" s="15">
+        <v>15.012308000000001</v>
+      </c>
+      <c r="Q192" s="16">
+        <v>1</v>
+      </c>
+      <c r="R192" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="S192" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A193" s="10"/>
+      <c r="B193" s="11"/>
+      <c r="C193" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D193" s="12">
+        <v>1</v>
+      </c>
+      <c r="E193" s="13">
+        <v>21</v>
+      </c>
+      <c r="F193" s="23">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="G193" s="23">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H193" s="23">
+        <v>1.02</v>
+      </c>
+      <c r="I193" s="23">
+        <v>0.98</v>
+      </c>
+      <c r="J193" s="23">
+        <v>0</v>
+      </c>
+      <c r="K193" s="23">
+        <v>0</v>
+      </c>
+      <c r="L193" s="23">
+        <v>1</v>
+      </c>
+      <c r="M193" s="14"/>
+      <c r="N193" s="14"/>
+      <c r="O193" s="15">
+        <v>48.39</v>
+      </c>
+      <c r="P193" s="15">
+        <v>15.049231000000001</v>
+      </c>
+      <c r="Q193" s="16">
+        <v>1</v>
+      </c>
+      <c r="R193" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="S193" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A194" s="10"/>
+      <c r="B194" s="11"/>
+      <c r="C194" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D194" s="12">
+        <v>1</v>
+      </c>
+      <c r="E194" s="13">
+        <v>21</v>
+      </c>
+      <c r="F194" s="23">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="G194" s="23">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H194" s="23">
+        <v>1.02</v>
+      </c>
+      <c r="I194" s="23">
+        <v>0.98</v>
+      </c>
+      <c r="J194" s="23">
+        <v>0</v>
+      </c>
+      <c r="K194" s="23">
+        <v>0</v>
+      </c>
+      <c r="L194" s="23">
+        <v>1</v>
+      </c>
+      <c r="M194" s="14"/>
+      <c r="N194" s="14"/>
+      <c r="O194" s="15">
+        <v>48.48</v>
+      </c>
+      <c r="P194" s="15">
+        <v>15.935385</v>
+      </c>
+      <c r="Q194" s="16">
+        <v>1</v>
+      </c>
+      <c r="R194" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="S194" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A195" s="10"/>
+      <c r="B195" s="11"/>
+      <c r="C195" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D195" s="12">
+        <v>1</v>
+      </c>
+      <c r="E195" s="13">
+        <v>21</v>
+      </c>
+      <c r="F195" s="23">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="G195" s="23">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H195" s="23">
+        <v>1.02</v>
+      </c>
+      <c r="I195" s="23">
+        <v>0.98</v>
+      </c>
+      <c r="J195" s="23">
+        <v>0</v>
+      </c>
+      <c r="K195" s="23">
+        <v>0</v>
+      </c>
+      <c r="L195" s="23">
+        <v>1</v>
+      </c>
+      <c r="M195" s="14"/>
+      <c r="N195" s="14"/>
+      <c r="O195" s="15">
+        <v>48.3</v>
+      </c>
+      <c r="P195" s="15">
+        <v>14.975384999999999</v>
+      </c>
+      <c r="Q195" s="16">
+        <v>1</v>
+      </c>
+      <c r="R195" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="S195" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A196" s="10"/>
+      <c r="B196" s="11"/>
+      <c r="C196" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D196" s="12">
+        <v>1</v>
+      </c>
+      <c r="E196" s="13">
+        <v>21</v>
+      </c>
+      <c r="F196" s="23">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="G196" s="23">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H196" s="23">
+        <v>1.02</v>
+      </c>
+      <c r="I196" s="23">
+        <v>0.98</v>
+      </c>
+      <c r="J196" s="23">
+        <v>0</v>
+      </c>
+      <c r="K196" s="23">
+        <v>0</v>
+      </c>
+      <c r="L196" s="23">
+        <v>1</v>
+      </c>
+      <c r="M196" s="14"/>
+      <c r="N196" s="14"/>
+      <c r="O196" s="15">
+        <v>48.39</v>
+      </c>
+      <c r="P196" s="15">
+        <v>15.418462</v>
+      </c>
+      <c r="Q196" s="16">
+        <v>1</v>
+      </c>
+      <c r="R196" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="S196" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A197" s="10"/>
+      <c r="B197" s="11"/>
+      <c r="C197" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="D197" s="12">
+        <v>1</v>
+      </c>
+      <c r="E197" s="13">
+        <v>21</v>
+      </c>
+      <c r="F197" s="23">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="G197" s="23">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H197" s="23">
+        <v>1.02</v>
+      </c>
+      <c r="I197" s="23">
+        <v>0.98</v>
+      </c>
+      <c r="J197" s="23">
+        <v>0</v>
+      </c>
+      <c r="K197" s="23">
+        <v>0</v>
+      </c>
+      <c r="L197" s="23">
+        <v>1</v>
+      </c>
+      <c r="M197" s="14"/>
+      <c r="N197" s="14"/>
+      <c r="O197" s="15">
+        <v>48.3</v>
+      </c>
+      <c r="P197" s="15">
+        <v>15.012308000000001</v>
+      </c>
+      <c r="Q197" s="16">
+        <v>1</v>
+      </c>
+      <c r="R197" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="S197" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A198" s="10"/>
+      <c r="B198" s="11"/>
+      <c r="C198" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="D198" s="12">
+        <v>1</v>
+      </c>
+      <c r="E198" s="13">
+        <v>21</v>
+      </c>
+      <c r="F198" s="23">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="G198" s="23">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H198" s="23">
+        <v>1.02</v>
+      </c>
+      <c r="I198" s="23">
+        <v>0.98</v>
+      </c>
+      <c r="J198" s="23">
+        <v>0</v>
+      </c>
+      <c r="K198" s="23">
+        <v>0</v>
+      </c>
+      <c r="L198" s="23">
+        <v>1</v>
+      </c>
+      <c r="M198" s="14"/>
+      <c r="N198" s="14"/>
+      <c r="O198" s="15">
+        <v>48.57</v>
+      </c>
+      <c r="P198" s="15">
+        <v>14.827692000000001</v>
+      </c>
+      <c r="Q198" s="16">
+        <v>1</v>
+      </c>
+      <c r="R198" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="S198" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A199" s="10"/>
+      <c r="B199" s="11"/>
+      <c r="C199" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="D199" s="12">
+        <v>1</v>
+      </c>
+      <c r="E199" s="13">
+        <v>21</v>
+      </c>
+      <c r="F199" s="23">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="G199" s="23">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H199" s="23">
+        <v>1.02</v>
+      </c>
+      <c r="I199" s="23">
+        <v>0.98</v>
+      </c>
+      <c r="J199" s="23">
+        <v>0</v>
+      </c>
+      <c r="K199" s="23">
+        <v>0</v>
+      </c>
+      <c r="L199" s="23">
+        <v>1</v>
+      </c>
+      <c r="M199" s="14"/>
+      <c r="N199" s="14"/>
+      <c r="O199" s="15">
+        <v>48.21</v>
+      </c>
+      <c r="P199" s="15">
+        <v>15.233846</v>
+      </c>
+      <c r="Q199" s="16">
+        <v>1</v>
+      </c>
+      <c r="R199" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="S199" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A200" s="10"/>
+      <c r="B200" s="11"/>
+      <c r="C200" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D200" s="12">
+        <v>1</v>
+      </c>
+      <c r="E200" s="13">
+        <v>21</v>
+      </c>
+      <c r="F200" s="23">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="G200" s="23">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H200" s="23">
+        <v>1.02</v>
+      </c>
+      <c r="I200" s="23">
+        <v>0.98</v>
+      </c>
+      <c r="J200" s="23">
+        <v>0</v>
+      </c>
+      <c r="K200" s="23">
+        <v>0</v>
+      </c>
+      <c r="L200" s="23">
+        <v>1</v>
+      </c>
+      <c r="M200" s="14"/>
+      <c r="N200" s="14"/>
+      <c r="O200" s="15">
         <v>48.22</v>
       </c>
-      <c r="P192" s="15">
+      <c r="P200" s="15">
         <v>15.3</v>
       </c>
-      <c r="Q192" s="16">
+      <c r="Q200" s="16">
         <v>2</v>
       </c>
-      <c r="R192" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="S192" s="17" t="s">
+      <c r="R200" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="S200" s="17" t="s">
         <v>67</v>
       </c>
     </row>
